--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,69 +466,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.490.000₫</t>
+          <t>24.490.000₫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26.490.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-03 08:57:25</t>
+          <t>2026-07-04 07:44:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.190.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -536,93 +536,89 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-03 08:57:37</t>
+          <t>2026-07-04 07:45:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.790.000₫</t>
+          <t>18.990.000₫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34.490.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-03 08:57:49</t>
+          <t>2026-07-04 07:45:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.790.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.090.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -630,46 +626,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:01</t>
+          <t>2026-07-04 07:45:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V15 ANV15-41-R732 (Ryzen 5 6600H/ RTX 4050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.790.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -680,39 +672,39 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 6600H (6 lõi / 12 luồng, 3.3 GHz - 4.5 GHz / 3 MB L2 cache, up to 16 MB L3 cache), 194 TOPs | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4 TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 57Whr 4-cell 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-41-r732</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:12</t>
+          <t>2026-07-04 07:45:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>22.890.000₫</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -723,39 +715,39 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency :3.6 GHz, Max Turbo Frequency : 4.8GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:23</t>
+          <t>2026-07-04 07:46:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite NL16-71G-71FN (I7-13620H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>20.990.000₫</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>31.990.000₫</t>
+          <t>25.490.000₫</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -766,39 +758,39 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (10 nhân, 16 luồng, Turbo tối đa Efficient-core: 3.6 GHz, Performance-core: 4.9 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB 2 khe (1 x 8GB Onboard + 1 x 8GB rời, nâng cấp lên tối đa 56GB (8GB Onboard + 48GB 1 thanh RAM rời) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB Gen4 NVMe) | Kích thước màn hình: 16 inch | Pin: 53Wh 3-cell Li-ion battery, 100W TypeC adapter | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-nl16-71g-71fn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:35</t>
+          <t>2026-07-04 07:46:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -806,46 +798,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:47</t>
+          <t>2026-07-04 07:46:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34.890.000₫</t>
+          <t>20.890.000₫</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -854,41 +842,37 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-03 08:58:59</t>
+          <t>2026-07-04 07:46:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>42.690.000₫</t>
+          <t>14.890.000₫</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>17.590.000₫</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -896,46 +880,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-03 08:59:10</t>
+          <t>2026-07-04 07:46:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-41-R7CR (Ryzen 5 7535HS/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27.790.000₫</t>
+          <t>14.390.000₫</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>15.450.000₫</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -943,46 +919,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5 7535HS ( 6 Nhân, 12 Luồng) Max. Boost Clock : Up to 4.55 GHz, 3MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W  USB Standard A  Three USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1 1x HDMI® 2.1 port with HDCP support 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, đèn nền đơn sắc (trắng) | Tản nhiệt: Dual-fan Dual-intake cooling system | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-03 08:59:23</t>
+          <t>2026-07-04 07:47:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>54.990.000₫</t>
+          <t>22.890.000₫</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>64.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -991,84 +963,84 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-03 08:59:34</t>
+          <t>2026-07-04 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90.490.000₫</t>
+          <t>17.490.000₫</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>93.580.000₫</t>
+          <t>20.490.000₫</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-03 08:59:46</t>
+          <t>2026-07-04 07:47:24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28.790.000₫</t>
+          <t>16.890.000₫</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.790.000₫</t>
+          <t>18.690.000₫</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1076,93 +1048,77 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-03 08:59:58</t>
+          <t>2026-07-04 07:47:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>49.990.000₫</t>
+          <t>17.990.000₫</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52.490.000₫</t>
+          <t>19.790.000₫</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-03 09:00:10</t>
+          <t>2026-07-04 07:47:51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25.190.000₫</t>
+          <t>19.490.000₫</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.690.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1171,41 +1127,37 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-03 09:00:27</t>
+          <t>2026-07-04 07:48:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>72.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>80.290.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1214,41 +1166,37 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-03 09:00:39</t>
+          <t>2026-07-04 07:48:14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75.990.000₫</t>
+          <t>14.190.000₫</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>83.590.000₫</t>
+          <t>16.990.000₫</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1257,41 +1205,37 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-03 09:00:51</t>
+          <t>2026-07-04 07:48:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
+          <t>15.890.000₫</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>69.990.000₫</t>
+          <t>16.990.000₫</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1302,39 +1246,39 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-03 09:01:03</t>
+          <t>2026-07-04 07:48:37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>49.990.000₫</t>
+          <t>18.490.000₫</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>50.990.000₫</t>
+          <t>20.490.000₫</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1345,39 +1289,39 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-03 09:01:15</t>
+          <t>2026-07-04 07:48:48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>44.890.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1389,34 +1333,34 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-03 09:01:27</t>
+          <t>2026-07-04 07:49:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>25.290.000₫</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1425,37 +1369,41 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-03 09:01:41</t>
+          <t>2026-07-04 07:49:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>36.990.000₫</t>
+          <t>27.990.000₫</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1464,162 +1412,166 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-03 09:01:52</t>
+          <t>2026-07-04 07:49:23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-03 09:02:04</t>
+          <t>2026-07-04 07:49:36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>49.990.000₫</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>53.990.000₫</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+          <t>40.990.000₫</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 7-350 (2.00GHz up to 5.00GHz, 16MB Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB (TGP: 100W – MGP: 115W) Hỗ trợ NVIDIA Advanced Optimus | RAM: 16GB (1x16GB) DDR5 5600MHz (Nâng cấp tối đa 96GB) | SSD: 512GB PCIe NVMe SSD (up to 4TB​) | Kích thước màn hình: 16 inch | Pin: 4Cell 76Wh | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-03 09:02:15</t>
+          <t>2026-07-04 07:49:51</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>26.890.000₫</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5 7640HS (Up to 5.0 GHz / 22MB /6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-03 09:02:27</t>
+          <t>2026-07-04 07:50:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>49.490.000₫</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>54.990.000₫</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1630,120 +1582,124 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-03 09:02:39</t>
+          <t>2026-07-04 07:50:18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>23.790.000₫</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>24.490.000₫</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-03 09:02:51</t>
+          <t>2026-07-04 07:50:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>33.490.000₫</t>
+          <t>31.490.000₫</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>32.490.000₫</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5-7640HS (Up to 5.0 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-03 09:03:03</t>
+          <t>2026-07-04 07:50:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34.490.000₫</t>
+          <t>31.490.000₫</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>35.490.000₫</t>
+          <t>32.490.000₫</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1753,83 +1709,91 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 7445HS (Up to 4.7 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-03 09:03:15</t>
+          <t>2026-07-04 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>43.290.000₫</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>41.990.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7, hỗ trợ 3328 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.4 kg</t>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-03 09:03:27</t>
+          <t>2026-07-04 07:51:11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>40.990.000₫</t>
+          <t>43.990.000₫</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>49.490.000₫</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1839,45 +1803,49 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, 1.6 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8 GB GDDR7, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery 135W_5.5PHY adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-03 09:03:39</t>
+          <t>2026-07-04 07:51:25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>53.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>62.090.000₫</t>
+          <t>27.990.000₫</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1888,17 +1856,17 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 7 350 (8 lõi / 16 luồng, 2 GHz - 5.0 GHz, 8MB L2 Cache 16MB L3 Cache) Up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8 GB GDDR7 VRAM, hỗ trợ 4608 NVIDIA CUDA Cores (798 AI GPU TOPs) | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: Li-ion Battery 76Wh 4-cell Li-ion battery 230W 5.5PHY Adapter | Trọng lượng: 2.18 kg</t>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-03 09:03:51</t>
+          <t>2026-07-04 07:51:40</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1878,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>33.890.000₫</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1920,7 +1888,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1941,29 +1909,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-03 09:04:03</t>
+          <t>2026-07-04 07:45:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>33.490.000₫</t>
+          <t>41.990.000₫</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>48.290.000₫</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1971,42 +1939,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency: 3.6 GHz, Max Turbo Frequency: 4.8 GHz, Bộ nhớ đệm Intel Smart Cache: 12 MB) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-03 09:04:15</t>
+          <t>2026-07-04 07:45:13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>32.990.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2014,42 +1986,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-03 09:04:27</t>
+          <t>2026-07-04 07:45:24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>36.990.000₫</t>
+          <t>50.990.000₫</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>58.690.000₫</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2057,42 +2033,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-03 09:04:39</t>
+          <t>2026-07-04 07:45:36</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>31.790.000₫</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>50.590.000₫</t>
+          <t>33.090.000₫</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2100,42 +2080,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-03 09:04:51</t>
+          <t>2026-07-04 07:45:48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>59.490.000₫</t>
+          <t>29.790.000₫</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>64.390.000₫</t>
+          <t>34.490.000₫</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2150,34 +2134,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-03 09:05:03</t>
+          <t>2026-07-04 07:46:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>41.990.000₫</t>
+          <t>34.890.000₫</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>48.290.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2192,83 +2176,87 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-03 09:05:15</t>
+          <t>2026-07-04 07:46:11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V 15 ANV15-41-R2UP (Ryzen 5 6600H/ RTX 2050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t>31.890.000₫</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>36.990.000₫</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5 6600H ( 6 Nhân, 12 Luồng, Up to 4.5 GHz) 3 MB L2 cache, up to 16 MB L3 cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 2050 with 4 GB of dedicated GDDR6 VRAM, supporting 2048 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD IPS 165Hz 45% NTSC 300nits, "Acer ComfyView™ LED-backlit TFT LCD 16:9 aspect ratio, supporting 144 Hz refresh rate. Wide viewing angle up to 170 degrees ,Ultra-slim design | Cổng giao tiếp: USB Type-C  USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W     USB Standard A   Three USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1     HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port   DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker Protection with up to 6 custom content modes by smart amplifier | Bàn phím: Led trắng | Đọc thẻ nhớ: None | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN Dual Band (2.4 GHz and 5 GHz) | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD audio/video recording | Hệ điều hành: Windows 11 Home | Pin: 57Whr 4-cell 135W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian Black | Chất liệu: Cover A, B, C, D: ABS Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-anv15-41-r2up</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-03 09:05:27</t>
+          <t>2026-07-04 07:46:22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>49.890.000₫</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>50.990.000₫</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>58.690.000₫</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2276,46 +2264,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-03 09:05:39</t>
+          <t>2026-07-04 07:46:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>59.890.000₫</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>69.990.000₫</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2323,46 +2307,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-03 09:05:51</t>
+          <t>2026-07-04 07:46:46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>48.790.000₫</t>
+          <t>54.890.000₫</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>50.990.000₫</t>
+          <t>64.990.000₫</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2370,46 +2350,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-03 09:06:02</t>
+          <t>2026-07-04 07:46:58</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>60.990.000₫</t>
+          <t>114.890.000₫</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>62.990.000₫</t>
+          <t>129.900.000₫</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2419,44 +2395,44 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-03 09:06:14</t>
+          <t>2026-07-04 07:47:10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48.490.000₫</t>
+          <t>75.890.000₫</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>52.990.000₫</t>
+          <t>83.590.000₫</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2464,46 +2440,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-03 09:06:26</t>
+          <t>2026-07-04 07:47:23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite 16 NL16-71G-71UJ (I7-13620H/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>72.890.000₫</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.090.000₫</t>
+          <t>80.290.000₫</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2511,46 +2483,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H (Upto 4.9 GHz/ 24MB/ 10 nhân, 16 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-03 09:06:38</t>
+          <t>2026-07-04 07:47:34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>114.990.000₫</t>
+          <t>60.890.000₫</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>129.900.000₫</t>
+          <t>62.990.000₫</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2560,44 +2528,44 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-03 09:06:49</t>
+          <t>2026-07-04 07:47:46</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>31.790.000₫</t>
+          <t>90.490.000₫</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>33.090.000₫</t>
+          <t>93.580.000₫</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2605,120 +2573,132 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-03 09:07:01</t>
+          <t>2026-07-04 07:47:58</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>49.990.000₫</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>87.990.000₫</t>
+          <t>52.490.000₫</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-03 09:07:13</t>
+          <t>2026-07-04 07:48:10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>31.990.000₫</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>27.540.000₫</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>30.300.000₫</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-03 09:07:28</t>
+          <t>2026-07-04 07:48:24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>53.140.000₫</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>58.460.000₫</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2727,37 +2707,41 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-03 09:07:40</t>
+          <t>2026-07-04 07:48:36</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>41.260.000₫</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>45.390.000₫</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2766,37 +2750,41 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-03 09:07:51</t>
+          <t>2026-07-04 07:48:48</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>36.990.000₫</t>
+          <t>28.790.000₫</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>37.990.000₫</t>
+          <t>30.790.000₫</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2804,38 +2792,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-03 09:08:03</t>
+          <t>2026-07-04 07:48:59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>86.990.000₫</t>
+          <t>32.190.000₫</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>87.990.000₫</t>
+          <t>34.590.000₫</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2846,33 +2842,41 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-03 09:08:14</t>
+          <t>2026-07-04 07:49:11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>199.990.000₫</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>33.190.000₫</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>35.590.000₫</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -2881,82 +2885,86 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-03 09:08:26</t>
+          <t>2026-07-04 07:49:23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>53.140.000₫</t>
+          <t>42.990.000₫</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.460.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-03 09:08:38</t>
+          <t>2026-07-04 07:49:36</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>41.260.000₫</t>
+          <t>42.660.000₫</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>45.390.000₫</t>
+          <t>44.990.000₫</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2964,42 +2972,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-03 09:08:57</t>
+          <t>2026-07-04 07:49:50</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>27.540.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>30.300.000₫</t>
+          <t>87.990.000₫</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3010,39 +3022,39 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-03 09:09:12</t>
+          <t>2026-07-04 07:50:01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>79.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>80.990.000₫</t>
+          <t>32.990.000₫</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3053,39 +3065,39 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-03 09:09:23</t>
+          <t>2026-07-04 07:50:13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>83.000.000₫</t>
+          <t>42.690.000₫</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>85.990.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3093,42 +3105,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-03 09:09:35</t>
+          <t>2026-07-04 07:50:25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>33.190.000₫</t>
+          <t>25.190.000₫</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>35.590.000₫</t>
+          <t>27.690.000₫</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3139,39 +3155,39 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-03 09:09:48</t>
+          <t>2026-07-04 07:50:36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>32.190.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>34.590.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3180,127 +3196,107 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:00</t>
+          <t>2026-07-04 07:50:48</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>42.660.000₫</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>44.990.000₫</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+          <t>31.990.000₫</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:11</t>
+          <t>2026-07-04 07:50:59</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>94.990.000₫</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>35.990.000₫</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:23</t>
+          <t>2026-07-04 07:51:11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>109.990.000₫</t>
+          <t>34.890.000₫</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>119.000.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3308,93 +3304,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:35</t>
+          <t>2026-07-04 07:51:23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>129.990.000₫</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>139.000.000₫</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+          <t>17.590.000₫</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:47</t>
+          <t>2026-07-04 07:44:55</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>67.690.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>73.990.000₫</t>
+          <t>30.490.000₫</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3402,46 +3386,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-03 09:10:59</t>
+          <t>2026-07-04 07:45:12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>61.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>62.990.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3453,73 +3429,69 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-03 09:11:10</t>
+          <t>2026-07-04 07:45:23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>83.990.000₫</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+          <t>199.990.000₫</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-03 09:11:22</t>
+          <t>2026-07-04 07:45:35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>27.890.000₫</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>32.090.000₫</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3530,39 +3502,39 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-03 09:11:33</t>
+          <t>2026-07-04 07:45:46</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>32.990.000₫</t>
+          <t>7.390.000₫</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>12.950.000₫</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-43%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3572,44 +3544,44 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-03 09:11:45</t>
+          <t>2026-07-04 07:45:58</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>23.490.000₫</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>24.290.000₫</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3619,263 +3591,263 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-03 09:12:00</t>
+          <t>2026-07-04 07:46:13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15.990.000₫</t>
+          <t>25.890.000₫</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>16.990.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-03 09:12:14</t>
+          <t>2026-07-04 07:46:28</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>19.990.000₫</t>
+          <t>23.490.000₫</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>26.490.000₫</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-03 09:12:26</t>
+          <t>2026-07-04 07:46:41</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17.490.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-03 09:12:37</t>
+          <t>2026-07-04 07:46:52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17.590.000₫</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+          <t>25.790.000₫</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>29.090.000₫</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
+          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-03 09:12:52</t>
+          <t>2026-07-04 07:47:05</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.390.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12.950.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-43%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-03 09:13:06</t>
+          <t>2026-07-04 07:47:17</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14.490.000₫</t>
+          <t>48.790.000₫</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15.450.000₫</t>
+          <t>50.990.000₫</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3883,42 +3855,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-03 09:13:20</t>
+          <t>2026-07-04 07:47:29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>19.990.000₫</t>
+          <t>59.490.000₫</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>64.390.000₫</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3926,42 +3902,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-03 09:13:32</t>
+          <t>2026-07-04 07:47:41</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15.990.000₫</t>
+          <t>43.890.000₫</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>16.990.000₫</t>
+          <t>50.590.000₫</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3970,37 +3950,41 @@
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-03 09:13:43</t>
+          <t>2026-07-04 07:47:52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18.990.000₫</t>
+          <t>24.390.000₫</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>28.190.000₫</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4008,42 +3992,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-03 09:13:55</t>
+          <t>2026-07-04 07:48:04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16-71G-71UJ (I7-13620H/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>17.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>19.790.000₫</t>
+          <t>30.090.000₫</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4051,33 +4039,41 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13620H (Upto 4.9 GHz/ 24MB/ 10 nhân, 16 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-03 09:14:10</t>
+          <t>2026-07-04 07:48:15</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite NL16-71G-71FN (I7-13620H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16.990.000₫</t>
+          <t>29.190.000₫</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>18.690.000₫</t>
+          <t>31.990.000₫</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4091,37 +4087,41 @@
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13620H (10 nhân, 16 luồng, Turbo tối đa Efficient-core: 3.6 GHz, Performance-core: 4.9 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB 2 khe (1 x 8GB Onboard + 1 x 8GB rời, nâng cấp lên tối đa 56GB (8GB Onboard + 48GB 1 thanh RAM rời) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB Gen4 NVMe) | Kích thước màn hình: 16 inch | Pin: 53Wh 3-cell Li-ion battery, 100W TypeC adapter | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-nl16-71g-71fn</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-03 09:14:22</t>
+          <t>2026-07-04 07:48:27</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15.990.000₫</t>
+          <t>49.990.000₫</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>17.590.000₫</t>
+          <t>53.990.000₫</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4130,131 +4130,127 @@
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 7-350 (2.00GHz up to 5.00GHz, 16MB Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB (TGP: 100W – MGP: 115W) Hỗ trợ NVIDIA Advanced Optimus | RAM: 16GB (1x16GB) DDR5 5600MHz (Nâng cấp tối đa 96GB) | SSD: 512GB PCIe NVMe SSD (up to 4TB​) | Kích thước màn hình: 16 inch | Pin: 4Cell 76Wh | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-03 09:14:33</t>
+          <t>2026-07-04 07:48:38</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming Acer Nitro V15 ANV15-41-R732 (Ryzen 5 6600H/ RTX 4050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18.990.000₫</t>
+          <t>25.890.000₫</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>19.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: AMD Ryzen 5 6600H (6 lõi / 12 luồng, 3.3 GHz - 4.5 GHz / 3 MB L2 cache, up to 16 MB L3 cache), 194 TOPs | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4 TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 57Whr 4-cell 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-41-r732</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-03 09:14:45</t>
+          <t>2026-07-04 07:48:50</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>27.990.000₫</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: AMD Ryzen™ 5 7640HS (Up to 5.0 GHz / 22MB /6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-03 09:15:00</t>
+          <t>2026-07-04 07:49:01</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>36.900.000₫</t>
+          <t>33.490.000₫</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>37.900.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4263,37 +4259,41 @@
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5-7640HS (Up to 5.0 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-03 09:15:14</t>
+          <t>2026-07-04 07:49:13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>34.490.000₫</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>35.490.000₫</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4304,34 +4304,34 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: AMD Ryzen™ 7 7445HS (Up to 4.7 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-03 09:15:25</t>
+          <t>2026-07-04 07:49:25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>33.900.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>34.900.000₫</t>
+          <t>36.990.000₫</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4345,36 +4345,32 @@
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-03 09:15:37</t>
+          <t>2026-07-04 07:49:37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>44.900.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>46.490.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4391,34 +4387,34 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-03 09:15:49</t>
+          <t>2026-07-04 07:49:49</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>41.990.000₫</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4427,37 +4423,41 @@
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7, hỗ trợ 3328 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.4 kg</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-03 09:16:01</t>
+          <t>2026-07-04 07:50:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>44.890.000₫</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4469,34 +4469,34 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-03 09:16:13</t>
+          <t>2026-07-04 07:50:12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>40.890.000₫</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4507,39 +4507,39 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, 1.6 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8 GB GDDR7, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery 135W_5.5PHY adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-03 09:16:25</t>
+          <t>2026-07-04 07:50:24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>53.990.000₫</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>30.490.000₫</t>
+          <t>62.090.000₫</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4548,76 +4548,80 @@
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 7 350 (8 lõi / 16 luồng, 2 GHz - 5.0 GHz, 8MB L2 Cache 16MB L3 Cache) Up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8 GB GDDR7 VRAM, hỗ trợ 4608 NVIDIA CUDA Cores (798 AI GPU TOPs) | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: Li-ion Battery 76Wh 4-cell Li-ion battery 230W 5.5PHY Adapter | Trọng lượng: 2.18 kg</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-03 09:16:37</t>
+          <t>2026-07-04 07:50:35</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro V 15 ANV15-41-R2UP (Ryzen 5 6600H/ RTX 2050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>35.990.000₫</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5 6600H ( 6 Nhân, 12 Luồng, Up to 4.5 GHz) 3 MB L2 cache, up to 16 MB L3 cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 2050 with 4 GB of dedicated GDDR6 VRAM, supporting 2048 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD IPS 165Hz 45% NTSC 300nits, "Acer ComfyView™ LED-backlit TFT LCD 16:9 aspect ratio, supporting 144 Hz refresh rate. Wide viewing angle up to 170 degrees ,Ultra-slim design | Cổng giao tiếp: USB Type-C  USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W     USB Standard A   Three USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1     HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port   DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker Protection with up to 6 custom content modes by smart amplifier | Bàn phím: Led trắng | Đọc thẻ nhớ: None | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN Dual Band (2.4 GHz and 5 GHz) | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD audio/video recording | Hệ điều hành: Windows 11 Home | Pin: 57Whr 4-cell 135W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian Black | Chất liệu: Cover A, B, C, D: ABS Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-anv15-41-r2up</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-03 09:16:49</t>
+          <t>2026-07-04 07:50:47</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-41-R7CR (Ryzen 5 7535HS/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>49.990.000₫</t>
+          <t>26.890.000₫</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>54.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4625,42 +4629,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: AMD Ryzen™ 5 7535HS ( 6 Nhân, 12 Luồng) Max. Boost Clock : Up to 4.55 GHz, 3MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W  USB Standard A  Three USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1 1x HDMI® 2.1 port with HDCP support 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, đèn nền đơn sắc (trắng) | Tản nhiệt: Dual-fan Dual-intake cooling system | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:00</t>
+          <t>2026-07-04 07:51:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>33.490.000₫</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4671,39 +4679,39 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency: 3.6 GHz, Max Turbo Frequency: 4.8 GHz, Bộ nhớ đệm Intel Smart Cache: 12 MB) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:12</t>
+          <t>2026-07-04 07:51:11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>27.890.000₫</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>25.490.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4714,39 +4722,39 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency :3.6 GHz, Max Turbo Frequency : 4.8GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:24</t>
+          <t>2026-07-04 07:51:23</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>48.490.000₫</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>25.290.000₫</t>
+          <t>52.990.000₫</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4754,42 +4762,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:36</t>
+          <t>2026-07-04 07:45:05</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>79.990.000₫</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>80.990.000₫</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4798,37 +4810,41 @@
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:48</t>
+          <t>2026-07-04 07:45:19</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20.990.000₫</t>
+          <t>83.000.000₫</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>85.990.000₫</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4837,37 +4853,41 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-03 09:17:59</t>
+          <t>2026-07-04 07:45:31</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20.990.000₫</t>
+          <t>67.690.000₫</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>73.990.000₫</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4875,154 +4895,174 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-03 09:18:11</t>
+          <t>2026-07-04 07:45:43</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>46.990.000₫</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>48.990.000₫</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+          <t>94.990.000₫</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-03 09:18:23</t>
+          <t>2026-07-04 07:45:56</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>40.990.000₫</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+          <t>129.990.000₫</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>139.000.000₫</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-03 09:18:34</t>
+          <t>2026-07-04 07:46:09</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>109.990.000₫</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>119.000.000₫</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-03 09:18:46</t>
+          <t>2026-07-04 07:46:21</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5035,42 +5075,46 @@
           <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-03 09:19:02</t>
+          <t>2026-07-04 07:46:35</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5080,44 +5124,44 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-03 09:19:16</t>
+          <t>2026-07-04 07:46:50</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37.990.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5127,44 +5171,44 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-03 09:19:30</t>
+          <t>2026-07-04 07:47:04</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>25.390.000₫</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>49.490.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5174,132 +5218,136 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-03 09:19:44</t>
+          <t>2026-07-04 07:47:18</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>23.790.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-03 09:19:59</t>
+          <t>2026-07-04 07:47:32</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>43.290.000₫</t>
+          <t>33.900.000₫</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>34.900.000₫</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-03 09:20:13</t>
+          <t>2026-07-04 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+          <t>36.900.000₫</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>37.900.000₫</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -5309,28 +5357,36 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-03 09:20:27</t>
+          <t>2026-07-04 07:48:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+          <t>44.900.000₫</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>46.490.000₫</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -5340,34 +5396,34 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-03 09:20:39</t>
+          <t>2026-07-04 07:48:11</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5378,34 +5434,34 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-03 09:20:51</t>
+          <t>2026-07-04 07:48:23</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>61.990.000₫</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>44.990.000₫</t>
+          <t>62.990.000₫</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5419,41 +5475,37 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-03 09:21:02</t>
+          <t>2026-07-04 07:48:35</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22.190.000₫</t>
+          <t>36.990.000₫</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>22.690.000₫</t>
+          <t>37.990.000₫</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5462,19 +5514,15 @@
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-03 09:21:14</t>
+          <t>2026-07-04 07:48:47</t>
         </is>
       </c>
     </row>
@@ -5513,29 +5561,29 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-03 09:21:26</t>
+          <t>2026-07-04 07:48:58</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>22.190.000₫</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>22.690.000₫</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5546,17 +5594,17 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-03 09:21:38</t>
+          <t>2026-07-04 07:49:10</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5631,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5603,29 +5651,29 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-03 09:21:50</t>
+          <t>2026-07-04 07:49:23</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>27.890.000₫</t>
+          <t>43.990.000₫</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>32.090.000₫</t>
+          <t>44.990.000₫</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5636,346 +5684,341 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-03 09:22:05</t>
+          <t>2026-07-04 07:49:39</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-03 09:22:17</t>
+          <t>2026-07-04 07:49:50</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>23.490.000₫</t>
+          <t>32.990.000₫</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>24.290.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-03 09:22:31</t>
+          <t>2026-07-04 07:50:03</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>37.990.000₫</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-03 09:22:45</t>
+          <t>2026-07-04 07:50:17</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>46.990.000₫</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>48.990.000₫</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-03 09:22:59</t>
+          <t>2026-07-04 07:50:31</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>29.990.000₫</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+          <t>59.990.000₫</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-03 09:23:13</t>
+          <t>2026-07-04 07:50:43</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>25.390.000₫</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>26.990.000₫</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+          <t>59.990.000₫</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-03 09:23:27</t>
+          <t>2026-07-04 07:50:55</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>42.990.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>83.990.000₫</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000₫ khi mua kèm 1 trong các sản phẩm: | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-03 09:23:42</t>
+          <t>2026-07-04 07:51:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>86.990.000₫</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>87.990.000₫</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-07-04 07:51:18</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,24 +466,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>26.990.000₫</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+          <t>17.590.000₫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -491,44 +483,44 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:42</t>
+          <t>2026-07-04 09:20:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>30.490.000₫</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -537,41 +529,37 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:59</t>
+          <t>2026-07-04 09:20:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.890.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -580,43 +568,31 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:11</t>
+          <t>2026-07-04 09:20:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.990.000₫</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25.490.000₫</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-18%</t>
-        </is>
-      </c>
+          <t>199.990.000₫</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -625,39 +601,39 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:23</t>
+          <t>2026-07-04 09:20:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20.890.000₫</t>
+          <t>27.890.000₫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>32.090.000₫</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,110 +642,130 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:35</t>
+          <t>2026-07-04 09:20:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22.890.000₫</t>
+          <t>7.390.000₫</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>12.950.000₫</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-43%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:48</t>
+          <t>2026-07-04 09:21:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>23.490.000₫</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>24.290.000₫</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:00</t>
+          <t>2026-07-04 09:21:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>25.890.000₫</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -779,174 +775,178 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:12</t>
+          <t>2026-07-04 09:21:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>23.490.000₫</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25.290.000₫</t>
+          <t>26.490.000₫</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:23</t>
+          <t>2026-07-04 09:21:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:35</t>
+          <t>2026-07-04 09:21:58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>25.790.000₫</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>29.090.000₫</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:48</t>
+          <t>2026-07-04 09:22:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -957,39 +957,39 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:38</t>
+          <t>2026-07-04 09:22:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25.490.000₫</t>
+          <t>48.790.000₫</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>50.990.000₫</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -997,38 +997,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:51</t>
+          <t>2026-07-04 09:22:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22.190.000₫</t>
+          <t>59.490.000₫</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22.690.000₫</t>
+          <t>64.390.000₫</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,89 +1044,89 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:03</t>
+          <t>2026-07-04 09:22:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>43.890.000₫</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.490.000₫</t>
+          <t>50.590.000₫</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:14</t>
+          <t>2026-07-04 09:22:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>24.390.000₫</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>44.990.000₫</t>
+          <t>28.190.000₫</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1126,42 +1134,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:30</t>
+          <t>2026-07-04 09:23:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16-71G-71UJ (I7-13620H/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>30.090.000₫</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1169,136 +1181,132 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ i7-13620H (Upto 4.9 GHz/ 24MB/ 10 nhân, 16 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:42</t>
+          <t>2026-07-04 09:23:18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop gaming Acer Nitro Lite NL16-71G-71FN (I7-13620H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32.990.000₫</t>
+          <t>29.190.000₫</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>31.990.000₫</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel Core i7-13620H (10 nhân, 16 luồng, Turbo tối đa Efficient-core: 3.6 GHz, Performance-core: 4.9 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB 2 khe (1 x 8GB Onboard + 1 x 8GB rời, nâng cấp lên tối đa 56GB (8GB Onboard + 48GB 1 thanh RAM rời) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB Gen4 NVMe) | Kích thước màn hình: 16 inch | Pin: 53Wh 3-cell Li-ion battery, 100W TypeC adapter | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-nl16-71g-71fn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:54</t>
+          <t>2026-07-04 09:23:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>37.990.000₫</t>
+          <t>49.990.000₫</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>53.990.000₫</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: AMD Ryzen™ AI 7-350 (2.00GHz up to 5.00GHz, 16MB Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB (TGP: 100W – MGP: 115W) Hỗ trợ NVIDIA Advanced Optimus | RAM: 16GB (1x16GB) DDR5 5600MHz (Nâng cấp tối đa 96GB) | SSD: 512GB PCIe NVMe SSD (up to 4TB​) | Kích thước màn hình: 16 inch | Pin: 4Cell 76Wh | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:08</t>
+          <t>2026-07-04 09:23:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop gaming Acer Nitro V15 ANV15-41-R732 (Ryzen 5 6600H/ RTX 4050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>46.990.000₫</t>
+          <t>25.890.000₫</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1309,179 +1317,207 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: AMD Ryzen 5 6600H (6 lõi / 12 luồng, 3.3 GHz - 4.5 GHz / 3 MB L2 cache, up to 16 MB L3 cache), 194 TOPs | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4 TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 57Whr 4-cell 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-41-r732</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:21</t>
+          <t>2026-07-04 09:23:52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>27.990.000₫</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5 7640HS (Up to 5.0 GHz / 22MB /6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:33</t>
+          <t>2026-07-04 09:24:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>33.490.000₫</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5-7640HS (Up to 5.0 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:45</t>
+          <t>2026-07-04 09:24:15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>40.990.000₫</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>34.490.000₫</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>35.490.000₫</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 7 7445HS (Up to 4.7 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:38</t>
+          <t>2026-07-04 09:24:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26.890.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>36.990.000₫</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:51</t>
+          <t>2026-07-04 09:24:38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>49.490.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>54.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1490,272 +1526,244 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:08</t>
+          <t>2026-07-04 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23.790.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>41.990.000₫</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7, hỗ trợ 3328 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.4 kg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:20</t>
+          <t>2026-07-04 09:25:01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>44.890.000₫</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:36</t>
+          <t>2026-07-04 09:25:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>40.890.000₫</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, 1.6 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8 GB GDDR7, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery 135W_5.5PHY adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:54</t>
+          <t>2026-07-04 09:25:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>43.290.000₫</t>
+          <t>53.990.000₫</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>62.090.000₫</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+          <t>CPU: AMD Ryzen AI 7 350 (8 lõi / 16 luồng, 2 GHz - 5.0 GHz, 8MB L2 Cache 16MB L3 Cache) Up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8 GB GDDR7 VRAM, hỗ trợ 4608 NVIDIA CUDA Cores (798 AI GPU TOPs) | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: Li-ion Battery 76Wh 4-cell Li-ion battery 230W 5.5PHY Adapter | Trọng lượng: 2.18 kg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:09</t>
+          <t>2026-07-04 09:25:35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Acer Nitro V 15 ANV15-41-R2UP (Ryzen 5 6600H/ RTX 2050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>49.490.000₫</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+          <t>CPU: AMD Ryzen™ 5 6600H ( 6 Nhân, 12 Luồng, Up to 4.5 GHz) 3 MB L2 cache, up to 16 MB L3 cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 2050 with 4 GB of dedicated GDDR6 VRAM, supporting 2048 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD IPS 165Hz 45% NTSC 300nits, "Acer ComfyView™ LED-backlit TFT LCD 16:9 aspect ratio, supporting 144 Hz refresh rate. Wide viewing angle up to 170 degrees ,Ultra-slim design | Cổng giao tiếp: USB Type-C  USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W     USB Standard A   Three USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1     HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port   DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker Protection with up to 6 custom content modes by smart amplifier | Bàn phím: Led trắng | Đọc thẻ nhớ: None | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN Dual Band (2.4 GHz and 5 GHz) | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD audio/video recording | Hệ điều hành: Windows 11 Home | Pin: 57Whr 4-cell 135W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian Black | Chất liệu: Cover A, B, C, D: ABS Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-anv15-41-r2up</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:23</t>
+          <t>2026-07-04 09:25:47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-41-R7CR (Ryzen 5 7535HS/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>26.890.000₫</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1763,42 +1771,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: AMD Ryzen™ 5 7535HS ( 6 Nhân, 12 Luồng) Max. Boost Clock : Up to 4.55 GHz, 3MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W  USB Standard A  Three USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1 1x HDMI® 2.1 port with HDCP support 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, đèn nền đơn sắc (trắng) | Tản nhiệt: Dual-fan Dual-intake cooling system | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:37</t>
+          <t>2026-07-04 09:25:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>33.490.000₫</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30.490.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1807,37 +1819,41 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency: 3.6 GHz, Max Turbo Frequency: 4.8 GHz, Bộ nhớ đệm Intel Smart Cache: 12 MB) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:49</t>
+          <t>2026-07-04 09:26:09</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>27.890.000₫</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1846,127 +1862,131 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency :3.6 GHz, Max Turbo Frequency : 4.8GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-04 08:54:01</t>
+          <t>2026-07-04 09:26:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27.890.000₫</t>
+          <t>24.490.000₫</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>32.090.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:41</t>
+          <t>2026-07-04 09:19:55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23.490.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>24.290.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-04 08:51:55</t>
+          <t>2026-07-04 09:20:11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>42.990.000₫</t>
+          <t>18.990.000₫</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1976,279 +1996,259 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:11</t>
+          <t>2026-07-04 09:20:22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:24</t>
+          <t>2026-07-04 09:20:35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:38</t>
+          <t>2026-07-04 09:20:47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>22.890.000₫</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-04 08:52:51</t>
+          <t>2026-07-04 09:20:59</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>25.390.000₫</t>
+          <t>20.990.000₫</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>25.490.000₫</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:08</t>
+          <t>2026-07-04 09:21:10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:22</t>
+          <t>2026-07-04 09:21:22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>33.900.000₫</t>
+          <t>20.890.000₫</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34.900.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2257,41 +2257,37 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:35</t>
+          <t>2026-07-04 09:21:33</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>36.900.000₫</t>
+          <t>14.890.000₫</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>37.900.000₫</t>
+          <t>17.590.000₫</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2303,51 +2299,3726 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-04 08:53:47</t>
+          <t>2026-07-04 09:21:45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>14.390.000₫</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15.450.000₫</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>22.890.000₫</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>23.990.000₫</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>17.490.000₫</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20.490.000₫</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16.890.000₫</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>18.690.000₫</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17.990.000₫</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>19.790.000₫</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19.490.000₫</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>21.990.000₫</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21.990.000₫</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>23.990.000₫</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>14.190.000₫</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16.990.000₫</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>15.890.000₫</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>16.990.000₫</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>18.490.000₫</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20.490.000₫</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22.990.000₫</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>23.990.000₫</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>22.990.000₫</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>25.290.000₫</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>24.990.000₫</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>27.990.000₫</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>28.990.000₫</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-17%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>40.990.000₫</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>26.890.000₫</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>30.990.000₫</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>49.490.000₫</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>54.990.000₫</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23.790.000₫</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>24.490.000₫</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>31.490.000₫</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>32.490.000₫</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>31.490.000₫</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>32.490.000₫</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>43.290.000₫</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>45.990.000₫</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:26:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>43.990.000₫</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>49.490.000₫</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>27.990.000₫</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>48.490.000₫</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>52.990.000₫</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:19:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>79.990.000₫</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>80.990.000₫</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>83.000.000₫</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>85.990.000₫</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>67.690.000₫</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>73.990.000₫</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>94.990.000₫</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>129.990.000₫</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>139.000.000₫</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>109.990.000₫</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>119.000.000₫</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>33.990.000₫</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>38.990.000₫</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>39.990.000₫</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>28.990.000₫</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>29.990.000₫</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>25.390.000₫</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>26.990.000₫</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>24.990.000₫</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>33.900.000₫</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>34.900.000₫</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>36.900.000₫</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>37.900.000₫</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>44.900.000₫</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>46.490.000₫</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>-3%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
         <is>
           <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:53:59</t>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>23.990.000₫</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>24.990.000₫</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>61.990.000₫</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>62.990.000₫</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>36.990.000₫</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>37.990.000₫</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>25.490.000₫</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>22.190.000₫</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>22.690.000₫</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20.490.000₫</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>22.490.000₫</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>43.990.000₫</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>44.990.000₫</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>33.990.000₫</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>32.990.000₫</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>39.990.000₫</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-18%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>37.990.000₫</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>39.990.000₫</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>46.990.000₫</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>48.990.000₫</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>59.990.000₫</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>59.990.000₫</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>82.990.000₫</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>83.990.000₫</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>86.990.000₫</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>87.990.000₫</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>33.890.000₫</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>40.290.000₫</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:19:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>41.990.000₫</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>48.290.000₫</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>39.990.000₫</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>45.990.000₫</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>50.990.000₫</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>58.690.000₫</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>31.790.000₫</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>33.090.000₫</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>29.790.000₫</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>34.490.000₫</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>34.890.000₫</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>39.990.000₫</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>31.890.000₫</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>36.990.000₫</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>49.890.000₫</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>50.990.000₫</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>59.890.000₫</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>69.990.000₫</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>54.890.000₫</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>64.990.000₫</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>114.890.000₫</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>129.900.000₫</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>75.890.000₫</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>83.590.000₫</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>72.890.000₫</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>80.290.000₫</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>60.890.000₫</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>62.990.000₫</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>90.490.000₫</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>93.580.000₫</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>49.990.000₫</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>52.490.000₫</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>27.540.000₫</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>30.300.000₫</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>53.140.000₫</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>58.460.000₫</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>41.260.000₫</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>45.390.000₫</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>28.790.000₫</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>30.790.000₫</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>32.190.000₫</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>34.590.000₫</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>33.190.000₫</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>35.590.000₫</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>42.990.000₫</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>82.990.000₫</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-48%</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>42.660.000₫</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>44.990.000₫</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>82.990.000₫</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>87.990.000₫</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>30.990.000₫</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>32.990.000₫</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>42.690.000₫</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>45.990.000₫</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>25.190.000₫</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>27.690.000₫</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>33.990.000₫</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>31.990.000₫</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:25:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>34.990.000₫</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>35.990.000₫</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>34.890.000₫</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>35.990.000₫</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:26:12</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -1881,69 +1881,65 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>33.890.000₫</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>40.290.000₫</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-05 01:49:43</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19.990.000₫</t>
+          <t>41.990.000₫</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>48.290.000₫</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1951,89 +1947,93 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:11</t>
+          <t>2026-07-05 01:49:55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19.990.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:22</t>
+          <t>2026-07-05 01:50:07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18.890.000₫</t>
+          <t>50.990.000₫</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>58.690.000₫</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2041,42 +2041,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:35</t>
+          <t>2026-07-05 01:50:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>31.790.000₫</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>33.090.000₫</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2084,42 +2088,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:47</t>
+          <t>2026-07-05 01:50:31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22.890.000₫</t>
+          <t>29.790.000₫</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>34.490.000₫</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2127,42 +2135,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:59</t>
+          <t>2026-07-05 01:50:42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20.990.000₫</t>
+          <t>34.890.000₫</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25.490.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2170,42 +2182,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:10</t>
+          <t>2026-07-05 01:50:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18.890.000₫</t>
+          <t>31.890.000₫</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>36.990.000₫</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2216,39 +2232,39 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:22</t>
+          <t>2026-07-05 01:51:06</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20.890.000₫</t>
+          <t>49.890.000₫</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>50.990.000₫</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2257,37 +2273,41 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:33</t>
+          <t>2026-07-05 01:51:18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14.890.000₫</t>
+          <t>59.890.000₫</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17.590.000₫</t>
+          <t>69.990.000₫</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2296,37 +2316,41 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:45</t>
+          <t>2026-07-05 01:51:29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14.390.000₫</t>
+          <t>54.890.000₫</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15.450.000₫</t>
+          <t>64.990.000₫</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2337,39 +2361,39 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:57</t>
+          <t>2026-07-05 01:51:41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22.890.000₫</t>
+          <t>114.890.000₫</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>129.900.000₫</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,85 +2401,89 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:08</t>
+          <t>2026-07-05 01:51:53</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17.490.000₫</t>
+          <t>75.890.000₫</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>83.590.000₫</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:20</t>
+          <t>2026-07-05 01:52:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16.890.000₫</t>
+          <t>72.890.000₫</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>18.690.000₫</t>
+          <t>80.290.000₫</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2464,37 +2492,41 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:33</t>
+          <t>2026-07-05 01:52:16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17.990.000₫</t>
+          <t>60.890.000₫</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>19.790.000₫</t>
+          <t>62.990.000₫</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2502,38 +2534,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:45</t>
+          <t>2026-07-05 01:52:28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19.490.000₫</t>
+          <t>90.490.000₫</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>93.580.000₫</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2542,76 +2582,88 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:59</t>
+          <t>2026-07-05 01:52:40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21.990.000₫</t>
+          <t>49.990.000₫</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>52.490.000₫</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:11</t>
+          <t>2026-07-05 01:52:52</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14.190.000₫</t>
+          <t>27.540.000₫</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>16.990.000₫</t>
+          <t>30.300.000₫</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2620,37 +2672,41 @@
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:23</t>
+          <t>2026-07-05 01:53:07</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15.890.000₫</t>
+          <t>53.140.000₫</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>16.990.000₫</t>
+          <t>58.460.000₫</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2661,39 +2717,39 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:34</t>
+          <t>2026-07-05 01:53:19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18.490.000₫</t>
+          <t>41.260.000₫</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>45.390.000₫</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2704,39 +2760,39 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:46</t>
+          <t>2026-07-05 01:53:30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>28.790.000₫</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>30.790.000₫</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2744,38 +2800,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:57</t>
+          <t>2026-07-05 01:53:42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22.990.000₫</t>
+          <t>32.190.000₫</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>25.290.000₫</t>
+          <t>34.590.000₫</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2786,39 +2850,39 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:10</t>
+          <t>2026-07-05 01:53:54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>33.190.000₫</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>35.590.000₫</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2829,39 +2893,39 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:21</t>
+          <t>2026-07-05 01:54:06</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>42.990.000₫</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2871,122 +2935,134 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:33</t>
+          <t>2026-07-05 01:54:19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>40.990.000₫</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>42.660.000₫</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>44.990.000₫</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:48</t>
+          <t>2026-07-05 01:54:33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26.890.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>87.990.000₫</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:59</t>
+          <t>2026-07-05 01:54:46</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>49.490.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>54.990.000₫</t>
+          <t>32.990.000₫</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2997,124 +3073,124 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:13</t>
+          <t>2026-07-05 01:54:57</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23.790.000₫</t>
+          <t>42.690.000₫</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>24.490.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:25</t>
+          <t>2026-07-05 01:55:09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>25.190.000₫</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>27.690.000₫</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:38</t>
+          <t>2026-07-05 01:55:21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>31.490.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>32.490.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3124,143 +3200,111 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:52</t>
+          <t>2026-07-05 01:55:33</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>43.290.000₫</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>45.990.000₫</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+          <t>31.990.000₫</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:06</t>
+          <t>2026-07-05 01:55:44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>49.490.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:17</t>
+          <t>2026-07-05 01:55:56</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>34.890.000₫</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>27.990.000₫</t>
+          <t>35.990.000₫</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3271,86 +3315,86 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:31</t>
+          <t>2026-07-05 01:56:08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>48.490.000₫</t>
+          <t>24.490.000₫</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>52.990.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:59</t>
+          <t>2026-07-04 09:19:55</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>79.990.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>80.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3361,82 +3405,86 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:12</t>
+          <t>2026-07-04 09:20:11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>83.000.000₫</t>
+          <t>18.990.000₫</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>85.990.000₫</t>
+          <t>19.990.000₫</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:23</t>
+          <t>2026-07-04 09:20:22</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>67.690.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>73.990.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3444,85 +3492,85 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:34</t>
+          <t>2026-07-04 09:20:35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>94.990.000₫</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+          <t>23.990.000₫</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>25.990.000₫</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:45</t>
+          <t>2026-07-04 09:20:47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>129.990.000₫</t>
+          <t>22.890.000₫</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>139.000.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3530,46 +3578,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-04 09:20:59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>109.990.000₫</t>
+          <t>20.990.000₫</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>119.000.000₫</t>
+          <t>25.490.000₫</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3577,113 +3621,97 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:08</t>
+          <t>2026-07-04 09:21:10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>18.890.000₫</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:19</t>
+          <t>2026-07-04 09:21:22</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>38.990.000₫</t>
+          <t>20.890.000₫</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3695,206 +3723,190 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28.990.000₫</t>
+          <t>14.890.000₫</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>29.990.000₫</t>
+          <t>17.590.000₫</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:46</t>
+          <t>2026-07-04 09:21:45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>25.390.000₫</t>
+          <t>14.390.000₫</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>26.990.000₫</t>
+          <t>15.450.000₫</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:59</t>
+          <t>2026-07-04 09:21:57</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>22.890.000₫</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:12</t>
+          <t>2026-07-04 09:22:08</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>33.900.000₫</t>
+          <t>17.490.000₫</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>34.900.000₫</t>
+          <t>20.490.000₫</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:25</t>
+          <t>2026-07-04 09:22:20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>36.900.000₫</t>
+          <t>16.890.000₫</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>37.900.000₫</t>
+          <t>18.690.000₫</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3906,34 +3918,34 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:36</t>
+          <t>2026-07-04 09:22:33</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>44.900.000₫</t>
+          <t>17.990.000₫</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>46.490.000₫</t>
+          <t>19.790.000₫</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3945,34 +3957,34 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:47</t>
+          <t>2026-07-04 09:22:45</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>23.990.000₫</t>
+          <t>19.490.000₫</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>24.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3981,41 +3993,37 @@
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:58</t>
+          <t>2026-07-04 09:22:59</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>61.990.000₫</t>
+          <t>21.990.000₫</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>62.990.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4027,34 +4035,34 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:09</t>
+          <t>2026-07-04 09:23:11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>36.990.000₫</t>
+          <t>14.190.000₫</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>37.990.000₫</t>
+          <t>16.990.000₫</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4066,34 +4074,34 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:21</t>
+          <t>2026-07-04 09:23:23</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>25.490.000₫</t>
+          <t>15.890.000₫</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>25.990.000₫</t>
+          <t>16.990.000₫</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4102,37 +4110,41 @@
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:32</t>
+          <t>2026-07-04 09:23:34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>22.190.000₫</t>
+          <t>18.490.000₫</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>22.690.000₫</t>
+          <t>20.490.000₫</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4143,86 +4155,78 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:43</t>
+          <t>2026-07-04 09:23:46</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20.490.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>22.490.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:55</t>
+          <t>2026-07-04 09:23:57</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>43.990.000₫</t>
+          <t>22.990.000₫</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>44.990.000₫</t>
+          <t>25.290.000₫</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4233,39 +4237,39 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:09</t>
+          <t>2026-07-04 09:24:10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>27.990.000₫</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4276,39 +4280,39 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:20</t>
+          <t>2026-07-04 09:24:21</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>32.990.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4318,107 +4322,95 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:31</t>
+          <t>2026-07-04 09:24:33</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>37.990.000₫</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>39.990.000₫</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+          <t>40.990.000₫</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:45</t>
+          <t>2026-07-04 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>46.990.000₫</t>
+          <t>26.890.000₫</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>48.990.000₫</t>
+          <t>30.990.000₫</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4430,256 +4422,296 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+          <t>49.490.000₫</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>54.990.000₫</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:10</t>
+          <t>2026-07-04 09:25:13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>59.990.000₫</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+          <t>23.790.000₫</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>24.490.000₫</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:21</t>
+          <t>2026-07-04 09:25:25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>31.490.000₫</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>83.990.000₫</t>
+          <t>32.490.000₫</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:32</t>
+          <t>2026-07-04 09:25:38</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>86.990.000₫</t>
+          <t>31.490.000₫</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>87.990.000₫</t>
+          <t>32.490.000₫</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:44</t>
+          <t>2026-07-04 09:25:52</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>33.890.000₫</t>
+          <t>43.290.000₫</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>40.290.000₫</t>
+          <t>45.990.000₫</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-04 09:26:06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>41.990.000₫</t>
+          <t>43.990.000₫</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>48.290.000₫</t>
+          <t>49.490.000₫</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:08</t>
+          <t>2026-07-04 09:26:17</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>27.990.000₫</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4687,46 +4719,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:21</t>
+          <t>2026-07-04 09:26:31</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>50.990.000₫</t>
+          <t>48.490.000₫</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>58.690.000₫</t>
+          <t>52.990.000₫</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4736,44 +4764,44 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:32</t>
+          <t>2026-07-05 01:50:27</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>31.790.000₫</t>
+          <t>79.990.000₫</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33.090.000₫</t>
+          <t>80.990.000₫</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4781,46 +4809,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:44</t>
+          <t>2026-07-05 01:50:41</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>29.790.000₫</t>
+          <t>83.000.000₫</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.490.000₫</t>
+          <t>85.990.000₫</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4828,46 +4852,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-05 01:50:53</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>34.890.000₫</t>
+          <t>67.690.000₫</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>39.990.000₫</t>
+          <t>73.990.000₫</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4877,87 +4897,83 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:07</t>
+          <t>2026-07-05 01:51:05</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31.890.000₫</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>36.990.000₫</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
+          <t>94.990.000₫</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:18</t>
+          <t>2026-07-05 01:51:17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>49.890.000₫</t>
+          <t>129.990.000₫</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>50.990.000₫</t>
+          <t>139.000.000₫</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4965,42 +4981,46 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:30</t>
+          <t>2026-07-05 01:51:29</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>59.890.000₫</t>
+          <t>109.990.000₫</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>69.990.000₫</t>
+          <t>119.000.000₫</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5008,260 +5028,276 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:42</t>
+          <t>2026-07-05 01:51:40</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>54.890.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>64.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:53</t>
+          <t>2026-07-05 01:51:53</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>114.890.000₫</t>
+          <t>38.990.000₫</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>129.900.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:04</t>
+          <t>2026-07-05 01:52:08</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>75.890.000₫</t>
+          <t>28.990.000₫</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>83.590.000₫</t>
+          <t>29.990.000₫</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:16</t>
+          <t>2026-07-05 01:52:22</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>72.890.000₫</t>
+          <t>25.390.000₫</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>80.290.000₫</t>
+          <t>26.990.000₫</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:28</t>
+          <t>2026-07-05 01:52:35</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>60.890.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.990.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:39</t>
+          <t>2026-07-05 01:52:49</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>90.490.000₫</t>
+          <t>33.900.000₫</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>93.580.000₫</t>
+          <t>34.900.000₫</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5277,86 +5313,78 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:50</t>
+          <t>2026-07-05 01:53:03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>49.990.000₫</t>
+          <t>36.900.000₫</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>52.490.000₫</t>
+          <t>37.900.000₫</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:02</t>
+          <t>2026-07-05 01:53:15</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>27.540.000₫</t>
+          <t>44.900.000₫</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>30.300.000₫</t>
+          <t>46.490.000₫</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5365,41 +5393,37 @@
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:16</t>
+          <t>2026-07-05 01:53:26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>53.140.000₫</t>
+          <t>23.990.000₫</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>58.460.000₫</t>
+          <t>24.990.000₫</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5410,39 +5434,39 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:28</t>
+          <t>2026-07-05 01:53:38</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>41.260.000₫</t>
+          <t>61.990.000₫</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>45.390.000₫</t>
+          <t>62.990.000₫</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5451,41 +5475,37 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:40</t>
+          <t>2026-07-05 01:53:50</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>28.790.000₫</t>
+          <t>36.990.000₫</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>30.790.000₫</t>
+          <t>37.990.000₫</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5493,46 +5513,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:51</t>
+          <t>2026-07-05 01:54:02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>32.190.000₫</t>
+          <t>25.490.000₫</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>34.590.000₫</t>
+          <t>25.990.000₫</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5541,41 +5553,37 @@
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:03</t>
+          <t>2026-07-05 01:54:14</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>33.190.000₫</t>
+          <t>22.190.000₫</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>35.590.000₫</t>
+          <t>22.690.000₫</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5586,39 +5594,39 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:14</t>
+          <t>2026-07-05 01:54:25</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>42.990.000₫</t>
+          <t>20.490.000₫</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>22.490.000₫</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5628,34 +5636,34 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:26</t>
+          <t>2026-07-05 01:54:37</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>42.660.000₫</t>
+          <t>43.990.000₫</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5665,7 +5673,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5673,46 +5681,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:40</t>
+          <t>2026-07-05 01:54:51</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>82.990.000₫</t>
+          <t>33.990.000₫</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>87.990.000₫</t>
+          <t>34.990.000₫</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5723,129 +5727,133 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:51</t>
+          <t>2026-07-05 01:55:02</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>30.990.000₫</t>
+          <t>32.990.000₫</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>32.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:02</t>
+          <t>2026-07-05 01:55:14</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>42.690.000₫</t>
+          <t>37.990.000₫</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>45.990.000₫</t>
+          <t>39.990.000₫</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:14</t>
+          <t>2026-07-05 01:55:27</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>25.190.000₫</t>
+          <t>46.990.000₫</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>27.690.000₫</t>
+          <t>48.990.000₫</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5856,41 +5864,33 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:25</t>
+          <t>2026-07-05 01:55:41</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>33.990.000₫</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>34.990.000₫</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+          <t>59.990.000₫</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -5900,24 +5900,24 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:37</t>
+          <t>2026-07-05 01:55:53</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>31.990.000₫</t>
+          <t>59.990.000₫</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -5931,34 +5931,34 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:48</t>
+          <t>2026-07-05 01:56:05</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>34.990.000₫</t>
+          <t>82.990.000₫</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>83.990.000₫</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5970,34 +5970,34 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:00</t>
+          <t>2026-07-05 01:56:17</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>34.890.000₫</t>
+          <t>86.990.000₫</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>35.990.000₫</t>
+          <t>87.990.000₫</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6008,17 +6008,17 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:12</t>
+          <t>2026-07-05 01:56:31</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1786,18 +1786,18 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>49490000</v>
+        <v>33890000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>54990000</v>
+        <v>40290000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1808,246 +1808,250 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:44</t>
+          <t>2026-07-06 12:12:33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>23790000</v>
+        <v>41990000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>24490000</v>
+        <v>48290000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:57</t>
+          <t>2026-07-06 12:12:44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>31490000</v>
+        <v>39990000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>32490000</v>
+        <v>45990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:12</t>
+          <t>2026-07-06 12:12:56</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>31490000</v>
+        <v>50990000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>32490000</v>
+        <v>58690000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:25</t>
+          <t>2026-07-06 12:13:08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>43290000</v>
+        <v>31790000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45990000</v>
+        <v>33090000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:39</t>
+          <t>2026-07-06 12:13:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>43990000</v>
+        <v>29790000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>49490000</v>
+        <v>34490000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:52</t>
+          <t>2026-07-06 12:13:32</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>25990000</v>
+        <v>34890000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>27990000</v>
+        <v>39990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2055,81 +2059,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:06</t>
+          <t>2026-07-06 12:13:44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>24490000</v>
+        <v>31890000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>26990000</v>
+        <v>36990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-06 12:13:55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>19990000</v>
+        <v>49890000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>21990000</v>
+        <v>50990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2140,78 +2144,74 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:11</t>
+          <t>2026-07-06 12:14:07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>18990000</v>
+        <v>59890000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>19990000</v>
+        <v>69990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:22</t>
+          <t>2026-07-06 12:14:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>18890000</v>
+        <v>54890000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>22990000</v>
+        <v>64990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2222,35 +2222,35 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:35</t>
+          <t>2026-07-06 12:14:31</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>23990000</v>
+        <v>114890000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>25990000</v>
+        <v>129900000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2258,38 +2258,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:47</t>
+          <t>2026-07-06 12:14:44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>22890000</v>
+        <v>75890000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>25990000</v>
+        <v>83590000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2300,74 +2304,78 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:59</t>
+          <t>2026-07-06 12:14:55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20990000</v>
+        <v>26890000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>25490000</v>
+        <v>30990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:10</t>
+          <t>2026-07-06 12:09:35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>18890000</v>
+        <v>49490000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>23990000</v>
+        <v>54990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2378,179 +2386,203 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:22</t>
+          <t>2026-07-06 12:09:52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>20890000</v>
+        <v>23790000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>21990000</v>
+        <v>24490000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:33</t>
+          <t>2026-07-06 12:10:04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>14890000</v>
+        <v>31490000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17590000</v>
+        <v>32490000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:45</t>
+          <t>2026-07-06 12:10:18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>14390000</v>
+        <v>31490000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>15450000</v>
+        <v>32490000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:57</t>
+          <t>2026-07-06 12:10:32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>22890000</v>
+        <v>43290000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>23990000</v>
+        <v>45990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:08</t>
+          <t>2026-07-06 12:10:47</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>17490000</v>
+        <v>43990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>20490000</v>
+        <v>49490000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2560,40 +2592,40 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:20</t>
+          <t>2026-07-06 12:11:01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>16890000</v>
+        <v>25990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>18690000</v>
+        <v>27990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2602,29 +2634,33 @@
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:33</t>
+          <t>2026-07-06 12:11:16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>17990000</v>
+        <v>24490000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>19790000</v>
+        <v>26990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
@@ -2633,37 +2669,45 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:45</t>
+          <t>2026-07-04 09:19:55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>19490000</v>
+        <v>19990000</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>21990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2672,68 +2716,80 @@
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:59</t>
+          <t>2026-07-04 09:20:11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>21990000</v>
+        <v>18990000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>23990000</v>
+        <v>19990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:11</t>
+          <t>2026-07-04 09:20:22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>14190000</v>
+        <v>18890000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>16990000</v>
+        <v>22990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2742,33 +2798,37 @@
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:23</t>
+          <t>2026-07-04 09:20:35</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>15890000</v>
+        <v>23990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>16990000</v>
+        <v>25990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2779,35 +2839,35 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:34</t>
+          <t>2026-07-04 09:20:47</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>18490000</v>
+        <v>22890000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>20490000</v>
+        <v>25990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2818,35 +2878,35 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:46</t>
+          <t>2026-07-04 09:20:59</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>22990000</v>
+        <v>20990000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>23990000</v>
+        <v>25490000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2855,33 +2915,37 @@
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:57</t>
+          <t>2026-07-04 09:21:10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>22990000</v>
+        <v>18890000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>25290000</v>
+        <v>23990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2892,35 +2956,35 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:10</t>
+          <t>2026-07-04 09:21:22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>24990000</v>
+        <v>20890000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>27990000</v>
+        <v>21990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2929,195 +2993,185 @@
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:21</t>
+          <t>2026-07-04 09:21:33</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>28990000</v>
+        <v>14890000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>34990000</v>
+        <v>17590000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:33</t>
+          <t>2026-07-04 09:21:45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
+        <v>14390000</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:48</t>
+          <t>2026-07-04 09:21:57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>26890000</v>
+        <v>22890000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>30990000</v>
+        <v>23990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:59</t>
+          <t>2026-07-04 09:22:08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>48490000</v>
+        <v>17490000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>52990000</v>
+        <v>20490000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:59</t>
+          <t>2026-07-04 09:22:20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>79990000</v>
+        <v>16890000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>80990000</v>
+        <v>18690000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3126,37 +3180,33 @@
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:12</t>
+          <t>2026-07-04 09:22:33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>83000000</v>
+        <v>17990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>85990000</v>
+        <v>19790000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3165,37 +3215,33 @@
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:23</t>
+          <t>2026-07-04 09:22:45</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>67690000</v>
+        <v>19490000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>73990000</v>
+        <v>21990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3203,79 +3249,69 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
-        </is>
-      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:34</t>
+          <t>2026-07-04 09:22:59</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>94990000</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
+        <v>21990000</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
-        </is>
-      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:45</t>
+          <t>2026-07-04 09:23:11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>129990000</v>
+        <v>14190000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>139000000</v>
+        <v>16990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3283,42 +3319,34 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
-        </is>
-      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-04 09:23:23</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>109990000</v>
+        <v>15890000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>119000000</v>
+        <v>16990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3326,214 +3354,190 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:08</t>
+          <t>2026-07-04 09:23:34</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>33990000</v>
+        <v>18490000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>34990000</v>
+        <v>20490000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:19</t>
+          <t>2026-07-04 09:23:46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>38990000</v>
+        <v>22990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>39990000</v>
+        <v>23990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:33</t>
+          <t>2026-07-04 09:23:57</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>28990000</v>
+        <v>22990000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>29990000</v>
+        <v>25290000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:46</t>
+          <t>2026-07-04 09:24:10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>25390000</v>
+        <v>24990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>26990000</v>
+        <v>27990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:59</t>
+          <t>2026-07-04 09:24:21</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>24990000</v>
+        <v>28990000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>25990000</v>
+        <v>34990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3543,75 +3547,65 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:12</t>
+          <t>2026-07-04 09:24:33</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:25</t>
+          <t>2026-07-04 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>36900000</v>
+        <v>33990000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>37900000</v>
+        <v>34990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
@@ -3620,33 +3614,41 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:36</t>
+          <t>2026-07-06 12:09:34</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>44900000</v>
+        <v>38990000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46490000</v>
+        <v>39990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
@@ -3655,146 +3657,174 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:47</t>
+          <t>2026-07-06 12:09:51</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>23990000</v>
+        <v>28990000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>24990000</v>
+        <v>29990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:58</t>
+          <t>2026-07-06 12:10:05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>61990000</v>
+        <v>25390000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>62990000</v>
+        <v>26990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:09</t>
+          <t>2026-07-06 12:10:20</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>36990000</v>
+        <v>24990000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>37990000</v>
+        <v>25990000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:21</t>
+          <t>2026-07-06 12:10:34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>25490000</v>
+        <v>33900000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>25990000</v>
+        <v>34900000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3803,33 +3833,37 @@
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:32</t>
+          <t>2026-07-06 12:10:49</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>22190000</v>
+        <v>36900000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22690000</v>
+        <v>37900000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3838,80 +3872,68 @@
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:43</t>
+          <t>2026-07-06 12:11:01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>20490000</v>
+        <v>44900000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>22490000</v>
+        <v>46490000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:55</t>
+          <t>2026-07-06 12:11:13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>43990000</v>
+        <v>23990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>44990000</v>
+        <v>24990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3922,35 +3944,35 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:09</t>
+          <t>2026-07-06 12:11:25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>33990000</v>
+        <v>61990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>34990000</v>
+        <v>62990000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3959,123 +3981,103 @@
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:20</t>
+          <t>2026-07-06 12:11:37</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>32990000</v>
+        <v>36990000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>39990000</v>
+        <v>37990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:31</t>
+          <t>2026-07-06 12:11:49</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>37990000</v>
+        <v>25490000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>39990000</v>
+        <v>25990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:45</t>
+          <t>2026-07-06 12:12:01</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46990000</v>
+        <v>22190000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>48990000</v>
+        <v>22690000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4086,93 +4088,117 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:59</t>
+          <t>2026-07-06 12:12:13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr"/>
+        <v>20490000</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>22490000</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:10</t>
+          <t>2026-07-06 12:12:24</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>44990000</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:21</t>
+          <t>2026-07-06 12:12:41</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>82990000</v>
+        <v>33990000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>83990000</v>
+        <v>34990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4181,111 +4207,123 @@
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:32</t>
+          <t>2026-07-06 12:12:53</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>86990000</v>
+        <v>32990000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>87990000</v>
+        <v>39990000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:44</t>
+          <t>2026-07-06 12:13:07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>75890000</v>
+        <v>37990000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>83590000</v>
+        <v>39990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:14</t>
+          <t>2026-07-06 12:13:22</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>72890000</v>
+        <v>46990000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>80290000</v>
+        <v>48990000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4296,160 +4334,128 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:25</t>
+          <t>2026-07-06 12:13:36</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>60890000</v>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>62990000</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
-        </is>
-      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:37</t>
+          <t>2026-07-06 12:13:48</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>90490000</v>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>93580000</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:18:48</t>
+          <t>2026-07-06 12:14:01</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>49990000</v>
+        <v>82990000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>52490000</v>
+        <v>83990000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:00</t>
+          <t>2026-07-06 12:14:13</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>27540000</v>
+        <v>86990000</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>30300000</v>
+        <v>87990000</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4460,35 +4466,35 @@
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:15</t>
+          <t>2026-07-06 12:14:24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>53140000</v>
+        <v>48490000</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>58460000</v>
+        <v>52990000</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4496,38 +4502,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:26</t>
+          <t>2026-07-04 09:19:59</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>41260000</v>
+        <v>79990000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>45390000</v>
+        <v>80990000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4538,35 +4548,35 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:38</t>
+          <t>2026-07-04 09:20:12</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>28790000</v>
+        <v>83000000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>30790000</v>
+        <v>85990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4574,42 +4584,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:19:49</t>
+          <t>2026-07-04 09:20:23</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>32190000</v>
+        <v>67690000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>34590000</v>
+        <v>73990000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4617,120 +4623,122 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:00</t>
+          <t>2026-07-04 09:20:34</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>33190000</v>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v>35590000</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>94990000</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:12</t>
+          <t>2026-07-04 09:20:45</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>42990000</v>
+        <v>129990000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>82990000</v>
+        <v>139000000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:23</t>
+          <t>2026-07-04 09:20:56</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>42660000</v>
+        <v>109990000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>44990000</v>
+        <v>119000000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4740,40 +4748,40 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:36</t>
+          <t>2026-07-04 09:21:08</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>82990000</v>
+        <v>72890000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>87990000</v>
+        <v>80290000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4784,35 +4792,35 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:48</t>
+          <t>2026-07-06 12:09:44</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>30990000</v>
+        <v>60890000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>32990000</v>
+        <v>62990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4820,38 +4828,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:59</t>
+          <t>2026-07-06 12:09:59</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>42690000</v>
+        <v>90490000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>45990000</v>
+        <v>93580000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4859,81 +4871,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:21:11</t>
+          <t>2026-07-06 12:10:12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>25190000</v>
+        <v>49990000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>27690000</v>
+        <v>52490000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:21:22</t>
+          <t>2026-07-06 12:10:23</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>33990000</v>
+        <v>27540000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>34990000</v>
+        <v>30300000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4942,62 +4954,76 @@
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:21:34</t>
+          <t>2026-07-06 12:10:39</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
+        <v>53140000</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>58460000</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:21:46</t>
+          <t>2026-07-06 12:10:50</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>34990000</v>
+        <v>41260000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>35990000</v>
+        <v>45390000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5006,33 +5032,37 @@
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:21:58</t>
+          <t>2026-07-06 12:11:02</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>34890000</v>
+        <v>28790000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>35990000</v>
+        <v>30790000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5040,38 +5070,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:22:09</t>
+          <t>2026-07-06 12:11:14</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>33890000</v>
+        <v>32190000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>40290000</v>
+        <v>34590000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5082,35 +5116,35 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-06 12:11:26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>41990000</v>
+        <v>33190000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>48290000</v>
+        <v>35590000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5118,85 +5152,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:08</t>
+          <t>2026-07-06 12:11:38</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>39990000</v>
+        <v>42990000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>45990000</v>
+        <v>82990000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:21</t>
+          <t>2026-07-06 12:11:49</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>50990000</v>
+        <v>42660000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>58690000</v>
+        <v>44990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5206,40 +5236,40 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:32</t>
+          <t>2026-07-06 12:12:04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>31790000</v>
+        <v>115990000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>33090000</v>
+        <v>117990000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5247,42 +5277,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:44</t>
+          <t>2026-07-06 12:12:15</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>29790000</v>
+        <v>30990000</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>34490000</v>
+        <v>32990000</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5290,42 +5316,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-06 12:12:28</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>34890000</v>
+        <v>42690000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>39990000</v>
+        <v>45990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5335,40 +5357,40 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:07</t>
+          <t>2026-07-06 12:12:39</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>31890000</v>
+        <v>25190000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>36990000</v>
+        <v>27690000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5379,35 +5401,35 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:18</t>
+          <t>2026-07-06 12:12:51</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>49890000</v>
+        <v>33990000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>50990000</v>
+        <v>34990000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5416,76 +5438,62 @@
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:30</t>
+          <t>2026-07-06 12:13:03</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>59890000</v>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>69990000</v>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:42</t>
+          <t>2026-07-06 12:13:14</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>54890000</v>
+        <v>34990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>64990000</v>
+        <v>35990000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5494,37 +5502,33 @@
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:53</t>
+          <t>2026-07-06 12:13:26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>114890000</v>
+        <v>34890000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>129900000</v>
+        <v>35990000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5532,24 +5536,90 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:04</t>
+          <t>2026-07-06 12:13:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:12:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:13:14</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1786,272 +1786,264 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>33890000</v>
+        <v>114890000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>40290000</v>
+        <v>129900000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:33</t>
+          <t>2026-07-08 17:44:41</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>41990000</v>
+        <v>75890000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>48290000</v>
+        <v>83590000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:44</t>
+          <t>2026-07-08 17:45:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>39990000</v>
+        <v>72890000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>45990000</v>
+        <v>80290000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:56</t>
+          <t>2026-07-08 17:45:14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>50990000</v>
+        <v>60890000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>58690000</v>
+        <v>62990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:08</t>
+          <t>2026-07-08 17:45:27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>31790000</v>
+        <v>90490000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>33090000</v>
+        <v>93580000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:20</t>
+          <t>2026-07-08 17:45:39</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>29790000</v>
+        <v>49990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>34490000</v>
+        <v>52490000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:32</t>
+          <t>2026-07-08 17:45:58</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>34890000</v>
+        <v>27540000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>39990000</v>
+        <v>30300000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2059,42 +2051,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:44</t>
+          <t>2026-07-08 17:46:17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>31890000</v>
+        <v>53140000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>36990000</v>
+        <v>58460000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2105,35 +2093,35 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:55</t>
+          <t>2026-07-08 17:46:37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>49890000</v>
+        <v>41260000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>50990000</v>
+        <v>45390000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2144,35 +2132,35 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:07</t>
+          <t>2026-07-08 17:46:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>59890000</v>
+        <v>28790000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>69990000</v>
+        <v>30790000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2180,38 +2168,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:19</t>
+          <t>2026-07-08 17:47:14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>54890000</v>
+        <v>32190000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>64990000</v>
+        <v>34590000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2222,35 +2214,35 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:31</t>
+          <t>2026-07-08 17:47:33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>114890000</v>
+        <v>33190000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>129900000</v>
+        <v>35590000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2258,124 +2250,124 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:44</t>
+          <t>2026-07-08 17:47:52</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>75890000</v>
+        <v>42990000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>83590000</v>
+        <v>82990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:55</t>
+          <t>2026-07-08 17:48:11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>26890000</v>
+        <v>42660000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>30990000</v>
+        <v>44990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:35</t>
+          <t>2026-07-08 17:48:29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>49490000</v>
+        <v>115990000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>54990000</v>
+        <v>117990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2386,246 +2378,220 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:52</t>
+          <t>2026-07-08 17:48:48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>23790000</v>
+        <v>30990000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>24490000</v>
+        <v>32990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:04</t>
+          <t>2026-07-08 17:49:07</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>31490000</v>
+        <v>42690000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>32490000</v>
+        <v>45990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:18</t>
+          <t>2026-07-08 17:49:25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>31490000</v>
+        <v>25190000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>32490000</v>
+        <v>27690000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:32</t>
+          <t>2026-07-08 17:49:43</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>43290000</v>
+        <v>33990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>45990000</v>
+        <v>34990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:47</t>
+          <t>2026-07-08 17:50:02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:01</t>
+          <t>2026-07-08 17:50:21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>25990000</v>
+        <v>34990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>27990000</v>
+        <v>35990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2634,80 +2600,72 @@
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:16</t>
+          <t>2026-07-08 17:50:39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>24490000</v>
+        <v>34890000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>26990000</v>
+        <v>35990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-08 17:50:58</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>19990000</v>
+        <v>48490000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>21990000</v>
+        <v>52990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2715,81 +2673,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:11</t>
+          <t>2026-07-08 17:51:17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>18990000</v>
+        <v>79990000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>19990000</v>
+        <v>80990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:22</t>
+          <t>2026-07-08 17:51:36</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>18890000</v>
+        <v>83000000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>22990000</v>
+        <v>85990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2800,35 +2758,35 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:35</t>
+          <t>2026-07-08 17:51:55</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>23990000</v>
+        <v>67690000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>25990000</v>
+        <v>73990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2836,77 +2794,79 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:47</t>
+          <t>2026-07-08 17:52:14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>22890000</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>94990000</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:59</t>
+          <t>2026-07-08 17:52:33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>20990000</v>
+        <v>129990000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>25490000</v>
+        <v>139000000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2914,73 +2874,73 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:10</t>
+          <t>2026-07-08 17:52:51</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>18890000</v>
+        <v>19490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>23990000</v>
+        <v>21990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:22</t>
+          <t>2026-07-09 00:04:17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>20890000</v>
+        <v>18990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>21990000</v>
+        <v>19990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -2989,329 +2949,333 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:33</t>
+          <t>2026-07-09 00:04:32</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>14890000</v>
+        <v>17990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>17590000</v>
+        <v>18990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:45</t>
+          <t>2026-07-09 00:04:44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>14390000</v>
+        <v>15990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>15450000</v>
+        <v>16990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:57</t>
+          <t>2026-07-09 00:04:56</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>22890000</v>
+        <v>21990000</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>23990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:08</t>
+          <t>2026-07-09 00:05:08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>17490000</v>
+        <v>14190000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>20490000</v>
+        <v>16990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:20</t>
+          <t>2026-07-09 00:05:21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>16890000</v>
+        <v>15890000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>18690000</v>
+        <v>16990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:33</t>
+          <t>2026-07-09 00:05:34</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>17990000</v>
+        <v>18490000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>19790000</v>
+        <v>20490000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:45</t>
+          <t>2026-07-09 00:05:46</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>19490000</v>
+        <v>22990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>21990000</v>
+        <v>23990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:59</t>
+          <t>2026-07-09 00:05:58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>21990000</v>
+        <v>24490000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>23990000</v>
+        <v>26990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:11</t>
+          <t>2026-07-04 09:19:55</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>14190000</v>
+        <v>19990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>16990000</v>
+        <v>21990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3320,72 +3284,80 @@
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:23</t>
+          <t>2026-07-04 09:20:11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>15890000</v>
+        <v>18990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>16990000</v>
+        <v>19990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:34</t>
+          <t>2026-07-04 09:20:22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>18490000</v>
+        <v>18890000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>20490000</v>
+        <v>22990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3396,35 +3368,35 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:46</t>
+          <t>2026-07-04 09:20:35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>22990000</v>
+        <v>23990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>23990000</v>
+        <v>25990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3433,33 +3405,37 @@
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:57</t>
+          <t>2026-07-04 09:20:47</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>22990000</v>
+        <v>22890000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>25290000</v>
+        <v>25990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3470,35 +3446,35 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:10</t>
+          <t>2026-07-04 09:20:59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>24990000</v>
+        <v>20990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>27990000</v>
+        <v>25490000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3509,74 +3485,76 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:21</t>
+          <t>2026-07-04 09:21:10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>28990000</v>
+        <v>18890000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>34990000</v>
+        <v>23990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:33</t>
+          <t>2026-07-04 09:21:22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
+        <v>20890000</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -3586,159 +3564,139 @@
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:48</t>
+          <t>2026-07-04 09:21:33</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>33990000</v>
+        <v>14890000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>34990000</v>
+        <v>17590000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:34</t>
+          <t>2026-07-04 09:21:45</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>38990000</v>
+        <v>14390000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>39990000</v>
+        <v>15450000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:51</t>
+          <t>2026-07-04 09:21:57</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>28990000</v>
+        <v>22890000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>29990000</v>
+        <v>23990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:05</t>
+          <t>2026-07-04 09:22:08</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>25390000</v>
+        <v>17490000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>26990000</v>
+        <v>20490000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3748,83 +3706,75 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:20</t>
+          <t>2026-07-04 09:22:20</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>24990000</v>
+        <v>16890000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>25990000</v>
+        <v>18690000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:34</t>
+          <t>2026-07-04 09:22:33</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>33900000</v>
+        <v>17990000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>34900000</v>
+        <v>19790000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3833,37 +3783,33 @@
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:49</t>
+          <t>2026-07-04 09:22:45</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>36900000</v>
+        <v>22990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>37900000</v>
+        <v>25290000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3872,33 +3818,37 @@
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:01</t>
+          <t>2026-07-04 09:24:10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>44900000</v>
+        <v>24990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>46490000</v>
+        <v>27990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3907,74 +3857,76 @@
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:13</t>
+          <t>2026-07-04 09:24:21</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>23990000</v>
+        <v>28990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>24990000</v>
+        <v>34990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:25</t>
+          <t>2026-07-04 09:24:33</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>62990000</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -3984,65 +3936,73 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:37</t>
+          <t>2026-07-04 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>36990000</v>
+        <v>26890000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>37990000</v>
+        <v>30990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:49</t>
+          <t>2026-07-04 09:24:59</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>25490000</v>
+        <v>49490000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>25990000</v>
+        <v>54990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4051,72 +4011,80 @@
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:01</t>
+          <t>2026-07-04 09:25:13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>22190000</v>
+        <v>23790000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>22690000</v>
+        <v>24490000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:13</t>
+          <t>2026-07-04 09:25:25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>20490000</v>
+        <v>31490000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>22490000</v>
+        <v>32490000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4124,120 +4092,124 @@
           <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:24</t>
+          <t>2026-07-04 09:25:38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>43990000</v>
+        <v>31490000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>44990000</v>
+        <v>32490000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:41</t>
+          <t>2026-07-04 09:25:52</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>33990000</v>
+        <v>43290000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>34990000</v>
+        <v>45990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:53</t>
+          <t>2026-07-04 09:26:06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>32990000</v>
+        <v>43990000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>39990000</v>
+        <v>49490000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4247,215 +4219,219 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:07</t>
+          <t>2026-07-04 09:26:17</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>37990000</v>
+        <v>25990000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>39990000</v>
+        <v>27990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:22</t>
+          <t>2026-07-04 09:26:31</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46990000</v>
+        <v>18990000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>48990000</v>
+        <v>19990000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:36</t>
+          <t>2026-07-08 17:47:47</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
+        <v>23990000</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:48</t>
+          <t>2026-07-08 17:48:44</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:01</t>
+          <t>2026-07-08 17:49:03</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>82990000</v>
+        <v>25990000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>83990000</v>
+        <v>26990000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:13</t>
+          <t>2026-07-08 17:49:22</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>86990000</v>
+        <v>109990000</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>87990000</v>
+        <v>119000000</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4463,116 +4439,124 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:14:24</t>
+          <t>2026-07-08 17:44:54</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>48490000</v>
+        <v>33990000</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>52990000</v>
+        <v>34990000</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:59</t>
+          <t>2026-07-08 17:45:07</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>79990000</v>
+        <v>38990000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>80990000</v>
+        <v>39990000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:12</t>
+          <t>2026-07-08 17:45:22</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>83000000</v>
+        <v>28990000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>85990000</v>
+        <v>29990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
@@ -4581,121 +4565,131 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:23</t>
+          <t>2026-07-08 17:45:35</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>67690000</v>
+        <v>25390000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>73990000</v>
+        <v>26990000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:34</t>
+          <t>2026-07-08 17:45:54</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>94990000</v>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:45</t>
+          <t>2026-07-08 17:46:13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>129990000</v>
+        <v>33900000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>139000000</v>
+        <v>34900000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4703,42 +4697,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-08 17:46:32</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>109990000</v>
+        <v>36900000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>119000000</v>
+        <v>37900000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4746,42 +4736,34 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
-        </is>
-      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:08</t>
+          <t>2026-07-08 17:46:51</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>72890000</v>
+        <v>44900000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>80290000</v>
+        <v>46490000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4790,37 +4772,33 @@
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:44</t>
+          <t>2026-07-08 17:47:10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>60890000</v>
+        <v>23990000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>62990000</v>
+        <v>24990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4828,42 +4806,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:09:59</t>
+          <t>2026-07-08 17:47:29</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>90490000</v>
+        <v>61990000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>93580000</v>
+        <v>62990000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4872,80 +4846,68 @@
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:12</t>
+          <t>2026-07-08 17:47:48</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>49990000</v>
+        <v>36990000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>52490000</v>
+        <v>37990000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:23</t>
+          <t>2026-07-08 17:48:07</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>27540000</v>
+        <v>25490000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>30300000</v>
+        <v>25990000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4954,37 +4916,33 @@
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:39</t>
+          <t>2026-07-08 17:48:26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>53140000</v>
+        <v>22190000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>58460000</v>
+        <v>22690000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4995,31 +4953,31 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:10:50</t>
+          <t>2026-07-08 17:48:45</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>41260000</v>
+        <v>20490000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>45390000</v>
+        <v>22490000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
@@ -5028,41 +4986,45 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:02</t>
+          <t>2026-07-08 17:49:04</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>28790000</v>
+        <v>43990000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>30790000</v>
+        <v>44990000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5070,42 +5032,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:14</t>
+          <t>2026-07-08 17:49:25</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>32190000</v>
+        <v>33990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>34590000</v>
+        <v>34990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5116,74 +5074,78 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:26</t>
+          <t>2026-07-08 17:49:44</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>33190000</v>
+        <v>32990000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>35590000</v>
+        <v>39990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:38</t>
+          <t>2026-07-08 17:50:03</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>42990000</v>
+        <v>37990000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>82990000</v>
+        <v>39990000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5193,40 +5155,40 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:11:49</t>
+          <t>2026-07-08 17:50:22</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>42660000</v>
+        <v>46990000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>44990000</v>
+        <v>48990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5234,120 +5196,96 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:04</t>
+          <t>2026-07-08 17:50:42</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>115990000</v>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>117990000</v>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:15</t>
+          <t>2026-07-08 17:51:01</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr"/>
+      <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:28</t>
+          <t>2026-07-08 17:51:19</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>42690000</v>
+        <v>82990000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>45990000</v>
+        <v>83990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5355,42 +5293,34 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
-        </is>
-      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:39</t>
+          <t>2026-07-08 17:51:38</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>25190000</v>
+        <v>86990000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>27690000</v>
+        <v>87990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5401,35 +5331,35 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:51</t>
+          <t>2026-07-08 17:51:57</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>33990000</v>
+        <v>33890000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>34990000</v>
+        <v>40290000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5438,62 +5368,80 @@
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:03</t>
+          <t>2026-07-04 09:19:55</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="2" t="inlineStr"/>
+        <v>41990000</v>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>48290000</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:14</t>
+          <t>2026-07-04 09:20:08</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>34990000</v>
+        <v>39990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>35990000</v>
+        <v>45990000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5501,34 +5449,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:26</t>
+          <t>2026-07-04 09:20:21</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>34890000</v>
+        <v>50990000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>35990000</v>
+        <v>58690000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5536,34 +5492,38 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:37</t>
+          <t>2026-07-04 09:20:32</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>24990000</v>
+        <v>31790000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>25990000</v>
+        <v>33090000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
@@ -5575,34 +5535,42 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:12:12</t>
+          <t>2026-07-04 09:20:44</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>18990000</v>
+        <v>29790000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>19990000</v>
+        <v>34490000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -5610,16 +5578,223 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:13:14</t>
+          <t>2026-07-04 09:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>34890000</v>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>31890000</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>49890000</v>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>50990000</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>59890000</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>69990000</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>54890000</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>64990000</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:21:53</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -497,14 +497,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17590000</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+        <v>24490000</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -512,40 +518,40 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
+          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:03</t>
+          <t>2026-07-09 08:13:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>29990000</v>
+        <v>19990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30490000</v>
+        <v>21990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -554,1053 +560,995 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:20</t>
+          <t>2026-07-09 08:13:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>34990000</v>
+        <v>18990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35990000</v>
+        <v>19990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:31</t>
+          <t>2026-07-09 08:13:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>199990000</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+        <v>18490000</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:42</t>
+          <t>2026-07-09 08:13:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>27890000</v>
+        <v>23990000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32090000</v>
+        <v>25990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:54</t>
+          <t>2026-07-09 08:14:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7390000</v>
+        <v>22890000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12950000</v>
+        <v>25990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:06</t>
+          <t>2026-07-09 08:14:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>23490000</v>
+        <v>20990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>24290000</v>
+        <v>25490000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
+          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:19</t>
+          <t>2026-07-09 08:14:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>25890000</v>
+        <v>18890000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>26990000</v>
+        <v>23990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:32</t>
+          <t>2026-07-09 08:14:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23490000</v>
+        <v>20890000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>26490000</v>
+        <v>21990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:44</t>
+          <t>2026-07-09 08:14:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>25990000</v>
+        <v>14890000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>29990000</v>
+        <v>17590000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:58</t>
+          <t>2026-07-09 08:15:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>25790000</v>
+        <v>18990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>29090000</v>
+        <v>19990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột Logitech G102 (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:10</t>
+          <t>2026-07-09 08:15:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>28990000</v>
+        <v>14390000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>33990000</v>
+        <v>15450000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:21</t>
+          <t>2026-07-09 08:15:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>48790000</v>
+        <v>22890000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>50990000</v>
+        <v>23990000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:33</t>
+          <t>2026-07-09 08:15:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>59490000</v>
+        <v>23990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>64390000</v>
+        <v>24990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:44</t>
+          <t>2026-07-09 08:15:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>43890000</v>
+        <v>24990000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>50590000</v>
+        <v>25990000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:55</t>
+          <t>2026-07-09 08:16:11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>24390000</v>
+        <v>25990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>28190000</v>
+        <v>26990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:07</t>
+          <t>2026-07-09 08:16:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite 16 NL16-71G-71UJ (I7-13620H/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>25990000</v>
+        <v>17490000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>30090000</v>
+        <v>20490000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H (Upto 4.9 GHz/ 24MB/ 10 nhân, 16 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:18</t>
+          <t>2026-07-09 08:16:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite NL16-71G-71FN (I7-13620H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>29190000</v>
+        <v>16890000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>31990000</v>
+        <v>18690000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-13620H (10 nhân, 16 luồng, Turbo tối đa Efficient-core: 3.6 GHz, Performance-core: 4.9 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB 2 khe (1 x 8GB Onboard + 1 x 8GB rời, nâng cấp lên tối đa 56GB (8GB Onboard + 48GB 1 thanh RAM rời) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB Gen4 NVMe) | Kích thước màn hình: 16 inch | Pin: 53Wh 3-cell Li-ion battery, 100W TypeC adapter | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-nl16-71g-71fn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:30</t>
+          <t>2026-07-09 08:16:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>49990000</v>
+        <v>17990000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>53990000</v>
+        <v>19790000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 7-350 (2.00GHz up to 5.00GHz, 16MB Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB (TGP: 100W – MGP: 115W) Hỗ trợ NVIDIA Advanced Optimus | RAM: 16GB (1x16GB) DDR5 5600MHz (Nâng cấp tối đa 96GB) | SSD: 512GB PCIe NVMe SSD (up to 4TB​) | Kích thước màn hình: 16 inch | Pin: 4Cell 76Wh | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:41</t>
+          <t>2026-07-09 08:17:02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V15 ANV15-41-R732 (Ryzen 5 6600H/ RTX 4050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>25890000</v>
+        <v>19490000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>30990000</v>
+        <v>21990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 5 6600H (6 lõi / 12 luồng, 3.3 GHz - 4.5 GHz / 3 MB L2 cache, up to 16 MB L3 cache), 194 TOPs | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4 TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 57Whr 4-cell 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-41-r732</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:52</t>
+          <t>2026-07-09 08:17:14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>27990000</v>
+        <v>18990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>34990000</v>
+        <v>19990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ 5 7640HS (Up to 5.0 GHz / 22MB /6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:04</t>
+          <t>2026-07-09 08:17:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>33490000</v>
+        <v>17990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>34990000</v>
+        <v>18990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ 5-7640HS (Up to 5.0 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:15</t>
+          <t>2026-07-09 08:17:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>34490000</v>
+        <v>15990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>35490000</v>
+        <v>16990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ 7 7445HS (Up to 4.7 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:27</t>
+          <t>2026-07-09 08:17:51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>35990000</v>
+        <v>21990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>36990000</v>
+        <v>23990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:38</t>
+          <t>2026-07-09 08:18:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>38990000</v>
+        <v>14190000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39990000</v>
+        <v>16990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:49</t>
+          <t>2026-07-09 08:18:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>38990000</v>
+        <v>15890000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>41990000</v>
+        <v>16990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7, hỗ trợ 3328 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.4 kg</t>
+          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:01</t>
+          <t>2026-07-09 08:18:29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>38990000</v>
+        <v>18490000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>44890000</v>
+        <v>20490000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:12</t>
+          <t>2026-07-09 08:18:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>40890000</v>
+        <v>22990000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>45990000</v>
+        <v>23990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, 1.6 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8 GB GDDR7, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery 135W_5.5PHY adapter | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:24</t>
+          <t>2026-07-09 08:18:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>53990000</v>
+        <v>129990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>62090000</v>
+        <v>139000000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1608,34 +1556,44 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen AI 7 350 (8 lõi / 16 luồng, 2 GHz - 5.0 GHz, 8MB L2 Cache 16MB L3 Cache) Up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8 GB GDDR7 VRAM, hỗ trợ 4608 NVIDIA CUDA Cores (798 AI GPU TOPs) | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: Li-ion Battery 76Wh 4-cell Li-ion battery 230W 5.5PHY Adapter | Trọng lượng: 2.18 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:35</t>
+          <t>2026-07-09 08:13:15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V 15 ANV15-41-R2UP (Ryzen 5 6600H/ RTX 2050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
+        <v>109990000</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
@@ -1643,278 +1601,290 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5 6600H ( 6 Nhân, 12 Luồng, Up to 4.5 GHz) 3 MB L2 cache, up to 16 MB L3 cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 2050 with 4 GB of dedicated GDDR6 VRAM, supporting 2048 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD IPS 165Hz 45% NTSC 300nits, "Acer ComfyView™ LED-backlit TFT LCD 16:9 aspect ratio, supporting 144 Hz refresh rate. Wide viewing angle up to 170 degrees ,Ultra-slim design | Cổng giao tiếp: USB Type-C  USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W     USB Standard A   Three USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1     HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port   DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker Protection with up to 6 custom content modes by smart amplifier | Bàn phím: Led trắng | Đọc thẻ nhớ: None | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN Dual Band (2.4 GHz and 5 GHz) | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD audio/video recording | Hệ điều hành: Windows 11 Home | Pin: 57Whr 4-cell 135W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian Black | Chất liệu: Cover A, B, C, D: ABS Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-anv15-41-r2up</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:47</t>
+          <t>2026-07-09 08:13:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-41-R7CR (Ryzen 5 7535HS/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>26890000</v>
+        <v>33990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>30990000</v>
+        <v>34990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 5 7535HS ( 6 Nhân, 12 Luồng) Max. Boost Clock : Up to 4.55 GHz, 3MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W  USB Standard A  Three USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1 1x HDMI® 2.1 port with HDCP support 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, đèn nền đơn sắc (trắng) | Tản nhiệt: Dual-fan Dual-intake cooling system | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:57</t>
+          <t>2026-07-09 08:13:41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>33490000</v>
+        <v>38990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>33990000</v>
+        <v>39990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency: 3.6 GHz, Max Turbo Frequency: 4.8 GHz, Bộ nhớ đệm Intel Smart Cache: 12 MB) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:09</t>
+          <t>2026-07-09 08:13:58</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>27890000</v>
+        <v>28990000</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>29990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency :3.6 GHz, Max Turbo Frequency : 4.8GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:20</t>
+          <t>2026-07-09 08:14:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>114890000</v>
+        <v>25390000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>129900000</v>
+        <v>26990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:44:41</t>
+          <t>2026-07-09 08:14:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>75890000</v>
+        <v>24990000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>83590000</v>
+        <v>25990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:00</t>
+          <t>2026-07-09 08:14:45</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>72890000</v>
+        <v>33900000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>80290000</v>
+        <v>34900000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:14</t>
+          <t>2026-07-09 08:14:59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>60890000</v>
+        <v>36900000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>62990000</v>
+        <v>37900000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -1923,41 +1893,33 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:27</t>
+          <t>2026-07-09 08:15:11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>90490000</v>
+        <v>44900000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>93580000</v>
+        <v>46490000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -1966,84 +1928,76 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:39</t>
+          <t>2026-07-09 08:15:22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>49990000</v>
+        <v>23990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>52490000</v>
+        <v>24990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:58</t>
+          <t>2026-07-09 08:15:34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>27540000</v>
+        <v>61990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>30300000</v>
+        <v>62990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2052,37 +2006,33 @@
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:17</t>
+          <t>2026-07-09 08:15:46</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>53140000</v>
+        <v>36990000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>58460000</v>
+        <v>37990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2091,37 +2041,33 @@
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:37</t>
+          <t>2026-07-09 08:15:57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>41260000</v>
+        <v>25490000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>45390000</v>
+        <v>25990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2130,37 +2076,33 @@
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:55</t>
+          <t>2026-07-09 08:16:09</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>28790000</v>
+        <v>22190000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>30790000</v>
+        <v>22690000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2168,81 +2110,81 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:14</t>
+          <t>2026-07-09 08:16:20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>32190000</v>
+        <v>20490000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>34590000</v>
+        <v>22490000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:33</t>
+          <t>2026-07-09 08:16:32</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>33190000</v>
+        <v>43990000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>35590000</v>
+        <v>44990000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2253,160 +2195,160 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:52</t>
+          <t>2026-07-09 08:16:46</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>42990000</v>
+        <v>33990000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>82990000</v>
+        <v>34990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:11</t>
+          <t>2026-07-09 08:16:57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>42660000</v>
+        <v>32990000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>44990000</v>
+        <v>39990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:29</t>
+          <t>2026-07-09 08:17:09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>115990000</v>
+        <v>37990000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>117990000</v>
+        <v>39990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:48</t>
+          <t>2026-07-09 08:17:21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>30990000</v>
+        <v>46990000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>32990000</v>
+        <v>48990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2417,117 +2359,93 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:07</t>
+          <t>2026-07-09 08:17:33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>42690000</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:25</t>
+          <t>2026-07-09 08:17:45</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>25190000</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>27690000</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:43</t>
+          <t>2026-07-09 08:17:56</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>33990000</v>
+        <v>82990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>34990000</v>
+        <v>83990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2539,254 +2457,262 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:02</t>
+          <t>2026-07-09 08:18:08</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
+        <v>86990000</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>87990000</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:21</t>
+          <t>2026-07-09 08:18:20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>34990000</v>
+        <v>22990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>35990000</v>
+        <v>25290000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:39</t>
+          <t>2026-07-09 08:13:09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>34890000</v>
+        <v>24990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>35990000</v>
+        <v>27990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:58</t>
+          <t>2026-07-09 08:13:27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>48490000</v>
+        <v>28990000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>52990000</v>
+        <v>34990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:17</t>
+          <t>2026-07-09 08:13:40</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>79990000</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>80990000</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:36</t>
+          <t>2026-07-09 08:13:53</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>83000000</v>
+        <v>26890000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>85990000</v>
+        <v>30990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:55</t>
+          <t>2026-07-09 08:14:05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>67690000</v>
+        <v>49490000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>73990000</v>
+        <v>54990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2794,445 +2720,467 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+      <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:52:14</t>
+          <t>2026-07-09 08:14:17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>94990000</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
+        <v>23790000</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>24490000</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:52:33</t>
+          <t>2026-07-09 08:14:29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>129990000</v>
+        <v>31490000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>139000000</v>
+        <v>32490000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:52:51</t>
+          <t>2026-07-09 08:14:41</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>19490000</v>
+        <v>31490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>21990000</v>
+        <v>32490000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:04:17</t>
+          <t>2026-07-09 08:14:54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>18990000</v>
+        <v>43290000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>19990000</v>
+        <v>45990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:04:32</t>
+          <t>2026-07-09 08:15:06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>17990000</v>
+        <v>43990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>18990000</v>
+        <v>49490000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:04:44</t>
+          <t>2026-07-09 08:15:20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>15990000</v>
+        <v>25990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>16990000</v>
+        <v>27990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:04:56</t>
+          <t>2026-07-09 08:15:38</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>17590000</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:05:08</t>
+          <t>2026-07-09 08:15:50</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>14190000</v>
+        <v>29990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>16990000</v>
+        <v>30490000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:05:21</t>
+          <t>2026-07-09 08:16:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>15890000</v>
+        <v>34990000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>16990000</v>
+        <v>35990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:05:34</t>
+          <t>2026-07-09 08:16:15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>18490000</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>20490000</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:05:46</t>
+          <t>2026-07-09 08:16:27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>22990000</v>
+        <v>27890000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>23990000</v>
+        <v>32090000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:05:58</t>
+          <t>2026-07-09 08:16:40</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>24490000</v>
+        <v>7390000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>26990000</v>
+        <v>12950000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-43%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3242,239 +3190,243 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-09 08:16:51</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>19990000</v>
+        <v>23490000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>21990000</v>
+        <v>24290000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:11</t>
+          <t>2026-07-09 08:17:04</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>18990000</v>
+        <v>25890000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>19990000</v>
+        <v>26990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:22</t>
+          <t>2026-07-09 08:17:20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>18890000</v>
+        <v>23490000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22990000</v>
+        <v>26490000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:35</t>
+          <t>2026-07-09 08:17:32</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>23990000</v>
+        <v>25990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>25990000</v>
+        <v>29990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:47</t>
+          <t>2026-07-09 08:17:45</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>22890000</v>
+        <v>25790000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>25990000</v>
+        <v>29090000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:59</t>
+          <t>2026-07-09 08:17:57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>20990000</v>
+        <v>28990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>25490000</v>
+        <v>33990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3485,524 +3437,566 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:10</t>
+          <t>2026-07-09 08:18:09</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>18890000</v>
+        <v>48790000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>23990000</v>
+        <v>50990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:22</t>
+          <t>2026-07-09 08:18:21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>20890000</v>
+        <v>59490000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>21990000</v>
+        <v>64390000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:33</t>
+          <t>2026-07-09 08:18:33</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>14890000</v>
+        <v>43890000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>17590000</v>
+        <v>50590000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:45</t>
+          <t>2026-07-09 08:18:46</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>14390000</v>
+        <v>24390000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>15450000</v>
+        <v>28190000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:57</t>
+          <t>2026-07-09 08:18:58</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>22890000</v>
+        <v>114890000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>23990000</v>
+        <v>129900000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:08</t>
+          <t>2026-07-09 08:13:15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>17490000</v>
+        <v>75890000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>20490000</v>
+        <v>83590000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:20</t>
+          <t>2026-07-09 08:13:30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>16890000</v>
+        <v>72890000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>18690000</v>
+        <v>80290000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:33</t>
+          <t>2026-07-09 08:13:44</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>17990000</v>
+        <v>60890000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>19790000</v>
+        <v>62990000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:45</t>
+          <t>2026-07-09 08:13:56</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>22990000</v>
+        <v>90490000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>25290000</v>
+        <v>93580000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:10</t>
+          <t>2026-07-09 08:14:08</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>24990000</v>
+        <v>49990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>27990000</v>
+        <v>52490000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:21</t>
+          <t>2026-07-09 08:14:20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>28990000</v>
+        <v>27540000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>34990000</v>
+        <v>30300000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:33</t>
+          <t>2026-07-09 08:14:32</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop gaming ASUS ROG Zephyrus G14 GA403WW QS136WS</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
+        <v>84990000</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>89490000</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 9 HX 370 | Card đồ họa: NVIDIA GeForce RTX 5080 | Tính chất bề mặt: ASUS | RAM: 64 | SSD: 2TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.57 kg</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g14-ga403ww-qs136ws</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:48</t>
+          <t>2026-07-09 08:14:45</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>26890000</v>
+        <v>53140000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>30990000</v>
+        <v>58460000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:59</t>
+          <t>2026-07-09 08:14:58</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>49490000</v>
+        <v>41260000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>54990000</v>
+        <v>45390000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4013,160 +4007,156 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:13</t>
+          <t>2026-07-09 08:15:10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>23790000</v>
+        <v>28790000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>24490000</v>
+        <v>30790000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:25</t>
+          <t>2026-07-09 08:15:30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>31490000</v>
+        <v>32190000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>32490000</v>
+        <v>34590000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:38</t>
+          <t>2026-07-09 08:15:42</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>31490000</v>
+        <v>33190000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>32490000</v>
+        <v>35590000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:52</t>
+          <t>2026-07-09 08:15:54</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>43290000</v>
+        <v>42990000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>45990000</v>
+        <v>82990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4176,83 +4166,83 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:06</t>
+          <t>2026-07-09 08:16:06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>43990000</v>
+        <v>42660000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>49490000</v>
+        <v>44990000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:17</t>
+          <t>2026-07-09 08:16:22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>25990000</v>
+        <v>115990000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>27990000</v>
+        <v>117990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4263,214 +4253,216 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:31</t>
+          <t>2026-07-09 08:16:33</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>18990000</v>
+        <v>30990000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>19990000</v>
+        <v>32990000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:47</t>
+          <t>2026-07-09 08:16:45</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>23990000</v>
+        <v>42690000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>24990000</v>
+        <v>45990000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:44</t>
+          <t>2026-07-09 08:16:57</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>24990000</v>
+        <v>25190000</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>25990000</v>
+        <v>27690000</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:03</t>
+          <t>2026-07-09 08:17:09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>25990000</v>
+        <v>33990000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>26990000</v>
+        <v>34990000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:22</t>
+          <t>2026-07-09 08:17:20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>109990000</v>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>119000000</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
-        </is>
-      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:44:54</t>
+          <t>2026-07-09 08:17:33</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>33990000</v>
+        <v>34990000</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>34990000</v>
+        <v>35990000</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
@@ -4479,41 +4471,33 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:07</t>
+          <t>2026-07-09 08:17:44</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>38990000</v>
+        <v>34890000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>39990000</v>
+        <v>35990000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
@@ -4522,174 +4506,162 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:22</t>
+          <t>2026-07-09 08:17:58</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>28990000</v>
+        <v>48490000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>29990000</v>
+        <v>52990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:35</t>
+          <t>2026-07-09 08:18:10</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>25390000</v>
+        <v>79990000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>26990000</v>
+        <v>80990000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:45:54</t>
+          <t>2026-07-09 08:18:24</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>24990000</v>
+        <v>83000000</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>25990000</v>
+        <v>85990000</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:13</t>
+          <t>2026-07-09 08:18:37</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>33900000</v>
+        <v>67690000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>34900000</v>
+        <v>73990000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4697,217 +4669,239 @@
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:32</t>
+          <t>2026-07-09 08:18:48</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>36900000</v>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>94990000</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:46:51</t>
+          <t>2026-07-09 08:19:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16-71G-71UJ (I7-13620H/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>44900000</v>
+        <v>25990000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>46490000</v>
+        <v>30090000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13620H (Upto 4.9 GHz/ 24MB/ 10 nhân, 16 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:10</t>
+          <t>2026-07-09 08:13:08</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite NL16-71G-71FN (I7-13620H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>23990000</v>
+        <v>29190000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>24990000</v>
+        <v>31990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel Core i7-13620H (10 nhân, 16 luồng, Turbo tối đa Efficient-core: 3.6 GHz, Performance-core: 4.9 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB 2 khe (1 x 8GB Onboard + 1 x 8GB rời, nâng cấp lên tối đa 56GB (8GB Onboard + 48GB 1 thanh RAM rời) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB Gen4 NVMe) | Kích thước màn hình: 16 inch | Pin: 53Wh 3-cell Li-ion battery, 100W TypeC adapter | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-nl16-71g-71fn</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:29</t>
+          <t>2026-07-09 08:13:24</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>61990000</v>
+        <v>49990000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>62990000</v>
+        <v>53990000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ AI 7-350 (2.00GHz up to 5.00GHz, 16MB Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB (TGP: 100W – MGP: 115W) Hỗ trợ NVIDIA Advanced Optimus | RAM: 16GB (1x16GB) DDR5 5600MHz (Nâng cấp tối đa 96GB) | SSD: 512GB PCIe NVMe SSD (up to 4TB​) | Kích thước màn hình: 16 inch | Pin: 4Cell 76Wh | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:47:48</t>
+          <t>2026-07-09 08:13:38</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop gaming Acer Nitro V15 ANV15-41-R732 (Ryzen 5 6600H/ RTX 4050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>36990000</v>
+        <v>25890000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>37990000</v>
+        <v>30990000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 6600H (6 lõi / 12 luồng, 3.3 GHz - 4.5 GHz / 3 MB L2 cache, up to 16 MB L3 cache), 194 TOPs | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4 TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 57Whr 4-cell 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-41-r732</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:07</t>
+          <t>2026-07-09 08:13:50</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>25490000</v>
+        <v>27990000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>25990000</v>
+        <v>34990000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4916,33 +4910,37 @@
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5 7640HS (Up to 5.0 GHz / 22MB /6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:26</t>
+          <t>2026-07-09 08:14:02</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>22190000</v>
+        <v>33490000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>22690000</v>
+        <v>34990000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4953,113 +4951,105 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
+          <t>CPU: AMD Ryzen™ 5-7640HS (Up to 5.0 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:48:45</t>
+          <t>2026-07-09 08:14:16</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>20490000</v>
+        <v>34490000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>22490000</v>
+        <v>35490000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+          <t>CPU: AMD Ryzen™ 7 7445HS (Up to 4.7 GHz / 22MB / 6 nhân, 12 luồng) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6GB of dedicated GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB PCIe Gen4 NVMe SSD) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:04</t>
+          <t>2026-07-09 08:14:30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>43990000</v>
+        <v>35990000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>44990000</v>
+        <v>36990000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:25</t>
+          <t>2026-07-09 08:14:42</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>33990000</v>
+        <v>38990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>34990000</v>
+        <v>39990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
@@ -5068,255 +5058,265 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:44</t>
+          <t>2026-07-09 08:14:56</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>32990000</v>
+        <v>38990000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>39990000</v>
+        <v>41990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7, hỗ trợ 3328 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.4 kg</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:03</t>
+          <t>2026-07-09 08:15:08</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>37990000</v>
+        <v>38990000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>39990000</v>
+        <v>44890000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:22</t>
+          <t>2026-07-09 08:15:21</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>46990000</v>
+        <v>40890000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>48990000</v>
+        <v>45990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, 1.6 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8 GB GDDR7, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery 135W_5.5PHY adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:50:42</t>
+          <t>2026-07-09 08:15:33</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr"/>
+        <v>53990000</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>62090000</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 7 350 (8 lõi / 16 luồng, 2 GHz - 5.0 GHz, 8MB L2 Cache 16MB L3 Cache) Up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8 GB GDDR7 VRAM, hỗ trợ 4608 NVIDIA CUDA Cores (798 AI GPU TOPs) | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: Li-ion Battery 76Wh 4-cell Li-ion battery 230W 5.5PHY Adapter | Trọng lượng: 2.18 kg</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:01</t>
+          <t>2026-07-09 08:15:45</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro V 15 ANV15-41-R2UP (Ryzen 5 6600H/ RTX 2050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>59990000</v>
+        <v>25990000</v>
       </c>
       <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5 6600H ( 6 Nhân, 12 Luồng, Up to 4.5 GHz) 3 MB L2 cache, up to 16 MB L3 cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 2050 with 4 GB of dedicated GDDR6 VRAM, supporting 2048 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD IPS 165Hz 45% NTSC 300nits, "Acer ComfyView™ LED-backlit TFT LCD 16:9 aspect ratio, supporting 144 Hz refresh rate. Wide viewing angle up to 170 degrees ,Ultra-slim design | Cổng giao tiếp: USB Type-C  USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W     USB Standard A   Three USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1     HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port   DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker Protection with up to 6 custom content modes by smart amplifier | Bàn phím: Led trắng | Đọc thẻ nhớ: None | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN Dual Band (2.4 GHz and 5 GHz) | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD audio/video recording | Hệ điều hành: Windows 11 Home | Pin: 57Whr 4-cell 135W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian Black | Chất liệu: Cover A, B, C, D: ABS Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-anv15-41-r2up</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:19</t>
+          <t>2026-07-09 08:15:59</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-41-R7CR (Ryzen 5 7535HS/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>82990000</v>
+        <v>26890000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>83990000</v>
+        <v>30990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen™ 5 7535HS ( 6 Nhân, 12 Luồng) Max. Boost Clock : Up to 4.55 GHz, 3MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 4800MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W  USB Standard A  Three USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1 featuring power off USB charging  • Two ports for USB 3.2 Gen 1 1x HDMI® 2.1 port with HDCP support 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, đèn nền đơn sắc (trắng) | Tản nhiệt: Dual-fan Dual-intake cooling system | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 23.5 (H) mm</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:38</t>
+          <t>2026-07-09 08:16:11</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>86990000</v>
+        <v>33490000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>87990000</v>
+        <v>33990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
@@ -5325,119 +5325,115 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency: 3.6 GHz, Max Turbo Frequency: 4.8 GHz, Bộ nhớ đệm Intel Smart Cache: 12 MB) | Card đồ họa: NVIDIA GeForce RTX 4050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:51:57</t>
+          <t>2026-07-09 08:16:24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>33890000</v>
+        <v>27890000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>40290000</v>
+        <v>29990000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng, Efficient-core Max Turbo Frequency :3.6 GHz, Max Turbo Frequency : 4.8GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:19:55</t>
+          <t>2026-07-09 08:16:38</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>41990000</v>
+        <v>33890000</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>48290000</v>
+        <v>40290000</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: Intel® Core™ 7 240H ( 2.5 GHz - 5.2 GHz / 24MB / 10 nhân, 16 luồng ) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB SSD M.2 NVMe ( 2 x M.2 NVMe ) | Kích thước màn hình: 15.6 inch | Pin: 4 cell 57 Wh | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:08</t>
+          <t>2026-07-09 08:16:51</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>39990000</v>
+        <v>41990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>45990000</v>
+        <v>48290000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
@@ -5446,41 +5442,41 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: AMD Ryzen™ 7 260 ( 8 nhân, 16 luồng) 8MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM, supporting 2560 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:21</t>
+          <t>2026-07-09 08:17:03</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>50990000</v>
+        <v>39990000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>58690000</v>
+        <v>45990000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
@@ -5489,7 +5485,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -5499,35 +5495,35 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
+          <t>CPU: AMD Ryzen™ AI 5 340( 6 nhân, 12 luồng) Max. Boost Clock : Up to 4.8 GHz, 6MB L2 Cache ; 16MB L3 Cache | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB | Màn hình: 16" FHD+ (1920x1200) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:32</t>
+          <t>2026-07-09 08:17:15</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>31790000</v>
+        <v>50990000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>33090000</v>
+        <v>58690000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -5542,83 +5538,83 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 16 luồng) Max. Boost Clock : Up to 5 GHz, 8MB L2 Cache ; 16MB L3 Cache | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPs | Màn hình: 16" 2K+ (2560x1600) IPS 180Hz,400nits,sRGB 100%,180Hz, High-brightness Acer ComfyView™ LED-backlit TFT LCD 3 ms (GTG) via LCD Overdrive Wide Viewing Angle Ultra-slim Design | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, Acer TrueHarmony Technology, Hi-Res Audio Certification by JAS | Bàn phím: 4 Zone RGB keyboard Nitro Sense Key Copilot Key Mode Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Killer™ Ethernet E2600 | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery 135W AC adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 357.7 (W) x 264 (D) x 13.9/19.95 (H) mm</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:44</t>
+          <t>2026-07-09 08:17:29</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-41-R7EN (Ryzen 7 8845HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>29790000</v>
+        <v>31790000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>34490000</v>
+        <v>33090000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: AMD Ryzen™ 7 8845HS (3.8 GHz upto 5.1 GHz, 8 nhân 16 luồng, 8 MB L2 cache, up to 16 MB L3 cache) | Ram: 32GB (2x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C™ port supporting:   • USB4® 40Gbps   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   Two USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 1   • One port for USB 3.2 Gen 2 featuring power off USB charging HDMI® 2.1 port with HDCP support   3.5 mm headphone/speaker jack, supporting headsets with built-in microphone   Ethernet (RJ-45) port | Audio: DTS® X:Ultra | Bàn phím: Amber-backlit keyboard | Tản nhiệt: 2 quạt | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Wi-Fi 6E Wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 4 Cell 57WHr | Trọng lượng: 2.5 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 361.8 (W) x 278.4 (D) x 24.74/25.46 (H) mm</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-anv16-41-r7en</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:20:56</t>
+          <t>2026-07-09 08:17:41</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-59AA (I5-13420H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>34890000</v>
+        <v>30890000</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>39990000</v>
+        <v>34490000</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -5628,173 +5624,216 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-13420H ( 8 nhân 12 luồng) Up to 4.6 GHz,12 MB Intel® Smart Cache | Ram: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-59aa</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:07</t>
+          <t>2026-07-09 08:17:54</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-72BM (I7-13620H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>31890000</v>
+        <v>34890000</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>36990000</v>
+        <v>39990000</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
+          <t>CPU: Intel® Core™ i7-13620H ( 10 nhân, 16 luồng) Up to 4.9 GHz, 24 MB Intel® Smart Cache | Ram: 16GB DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe M2, max 2 TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 | Màn hình: 15.6" FHD (1920x1200) IPS,  180Hz , 300nits, 100% sRGB,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C  1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C via iGPU  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 65 W    USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1 featuring power off USB charging  • 2x ports for USB 3.2 Gen 1    1x HDMI® 2.1 port with HDCP support    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone    1x Ethernet (RJ-45) port    1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, Amber-backlit keyboard NitroSense Key Copilot Key | Tản nhiệt: Dual-fan | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.1 | Webcam: 720p HD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  135W 5.5PHY Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Plastic | Kích thước: 362.3 (W) x 239.89 (D) x 15.7/23.5 (H) mm</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-72bm</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:18</t>
+          <t>2026-07-09 08:18:06</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>49890000</v>
+        <v>31890000</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>50990000</v>
+        <v>36990000</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, tần số cơ bản 1.8 GHz, Turbo tối đa 5.2 GHz, 24 MB Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 57 Wh 4-cell Li-ion batter 135W 5.5PHY Adapter | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:30</t>
+          <t>2026-07-09 08:18:19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-50H7 (I5-14450HX/ RTX 5050 8GB/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>59890000</v>
+        <v>49890000</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>69990000</v>
+        <v>50990000</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+          <t>CPU: Intel® Core™ i5-14450HX (10 nhân / 16 luồng / 1.8 GHz - 4.8 GHz / 20MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 8GB GDDR7 (2560 CUDA cores) | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM / up to 96GB) | SSD: 512GB PCIe NVMe M.2 SSD (2 Khe cắm M.2 2280 / tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 92WHrs / 4-cell Li-ion | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-50h7</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:42</t>
+          <t>2026-07-09 08:18:32</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-72XE (I7-14650HX/ RTX 5060 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>54890000</v>
+        <v>59890000</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>64990000</v>
+        <v>69990000</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
+          <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, 572 TOPs | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-72xe</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:18:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>54890000</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>64990000</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
           <t>CPU: Intel® Core™ i7-14650HX (16 nhân, 24 luồng, turbo max 5,2GHz, 30mb) | Card đồ họa: NVIDIA® GeForce RTX™ 5050 with 8 GB of dedicated GDDR7 VRAM | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.5 kg</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-04 09:21:53</t>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:18:57</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -497,57 +497,57 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24490000</v>
+        <v>114890000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>26990000</v>
+        <v>129900000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen™ AI 5 340 ( 6 nhân, 12 luồng) Up to 4.8 GHz, 6 MB L2 Cache, 16MB L3 Cache Up to 50 TOPS | VGA: AMD Radeon™ 840M Graphics | RAM: 16GB DDR5 Up to 8533 MT/s ( Không nâng cấp) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 65Wh 4-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.25 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 processor 275HX (up to 5.4Ghz, 24 Core 24 Threads, 36MB cache) , 13 TOPS | RAM: 64GB (32GBx2) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 2TB (1TB x 2) M.2 NVMe ( Total 2 Slot) | VGA: NVIDIA® GeForce RTX™ 5070 Ti with 12 GB of dedicated GDDR7 VRAM, supporting 5888 NVIDIA® CUDA® Cores. | Màn hình: 16" 2K+ (2560 x 1600) OLED, 500 nits, 240Hz, 100% DCI-P3, AcerCineCrystal™ True Black HDR 500 ,Nvidia Advanced Optimus capable | Cổng giao tiếp: 1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    3x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2  • One port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support  1x Ethernet (RJ-45) port  1x Micro SD card reader   1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Chuẩn LAN: Killer Ethernet E3100G | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.4 | Webcam: • Narrow USB FHD camera+IR camera with blue glass  • Compatible with Windows only  • 1920 x 1080 resolution  • 1080p HD video at 60 fps with Temporal Noise Reduction  • Blue glass lens  • Staggered High Dynamic Range (SHDR)  • Dual Mic (33 mm + 33 mm)  • 88 x 3.2 x 2.6 mm | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.3 kg | Màu sắc: Abyssal black | Chất liệu: Cover A, D: Metal  Cover B, C: ABS Plastic | Kích thước: 55.0 (L) x 8.7 (W) x 34.7 (H) cm</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-ai-a14-61m-r9ra</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:05</t>
+          <t>2026-07-10 08:02:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19990000</v>
+        <v>75890000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>21990000</v>
+        <v>83590000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -556,380 +556,400 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>CPU: Qualcomm Snapdragon X X1-26100 8C (8 lõi / 16 luồng, 2.0 GHz - 3.0 GHz, 30MB Cache) Up to 45 TOPS | VGA: Card đồ họa tích hợp - Qualcomm® Adreno™ | RAM: 16 GB Onboard (LPDDR5X Memory) - Không có khe RAM, chỉ có RAM onboard | Kích thước màn hình: 14 inch | Pin: 65Wh 3-cell Li-ion battery 65W TypeC adapter | Trọng lượng: 1.26 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:22</t>
+          <t>2026-07-10 08:02:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 5 A515 58GM 59LJ</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18990000</v>
+        <v>72890000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19990000</v>
+        <v>80290000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-13420H | VGA: RTX 2050 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H (18MB Cache, 2.1 GHz up to 4.9 GHz, 16 nhân, 16 luồng) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM | RAM: 16GB (2 x 8GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 16 inch | Pin: 4 | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-5-a515-58gm-59lj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:34</t>
+          <t>2026-07-10 08:02:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios PHN16-73-757W (Ultra 7-255HX/ RTX 5060/ 32GB/ 1TB/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18490000</v>
+        <v>60890000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>22990000</v>
+        <v>62990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 nhân / 12 luồng, 0.9 GHz - 5.0 GHz, 12 MB Intel Smart Cache) | VGA: Intel UHD Graphics | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3 Cell Li-ion | Trọng lượng: 1.4 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255HX ( 20 nhân, 20 luồng) up to 5.2 GHz, 30MB Cache, 13 TOPS | RAM: 32GB (1x32GB) DDR5 6400MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 1TB PCIe NVMe SED SSD (Còn trống 1 khe SSD M.2 PCIE Gen 4, nâng cấp tối đa 4TB SSD PCIe Gen 4) | VGA: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores, 572 TOPS | Màn hình: 16" 2K+ (2560 x 1600) 240Hz DCI-P3 100% DDS, 500nits, Acer ComfyView™ LED-backlit TFT LCD,Nvidia Advanced Optimus capable,Wide viewing angle,Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 or 100 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 3.2 Gen 1  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging    1x HDMI® 2.1 port with HDCP support    1x Ethernet (RJ-45) port    1x microSD card (SDXC compatible)    1x DC-in jack for AC adapter    1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: Full size, RGB 4 Zone | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen + Plastic Fan)  Vector heat pipes  Liquid Metal Thermal Grease | Chuẩn  LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax wireless LAN | Bluetooth: v5.4 | Webcam: • Narrow USB HD camera • 1280 x 720 resolution • 1080p HD video at 60 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Pin: 90Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.8 kg | Màu sắc: Obsidian black | Chất liệu: Cover A: Aluminium  Cover B,C,D: ABS Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 13.47/23.90 (H) mm</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-phn16-73-757w</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:49</t>
+          <t>2026-07-10 08:02:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070/ 32GB/ 2TB/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>23990000</v>
+        <v>90490000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25990000</v>
+        <v>93580000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 125H 1.2 GHz (18MB Cache, up to 4.5 GHz, 14 cores, 18 Threads) | VGA: Intel® ARC™ Graphics | RAM: 16 GB LPDDR5X | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 55Wh 3-cell | Trọng lượng: 1.49 kg kg</t>
+          <t>CPU: Intel® Core™ Ultra 9 288V (8 nhân 8 luồng, Max Turbo ~5.1 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 8 GB GDDR7 (798 AI TOPS) | RAM: 32 GB LPDDR5X onboard | SSD: 2 TB PCIe NVMe SED SSD | Kích thước màn hình: 14.5 inch | Pin: 4 | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:01</t>
+          <t>2026-07-10 08:03:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>22890000</v>
+        <v>49990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>25990000</v>
+        <v>52490000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 7 150U (1.8 GHz - 5.4 GHz / 12MB / 10 nhân / 12 luồng) Non-EVO | VGA: Intel UHD Graphics | RAM: 16GB (1 x 16GB) DDR4 3200MHz (2 khe / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell / Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 Processor 155H, 16 nhân 22 luồng, upto 3.8Ghz - 4.8Ghz, 24 MB Intel® Smart Cache | RAM: 32GB (1*32GB) LPDDR5X 7467Mhz (Không nâng cấp) | Ổ cứng: 2TB PCIe NVMe SED SSD (nâng cấp tối đa 2TB SSD) | VGA: NVIDIA® GeForce RTX™ 4060 with 8 GB of dedicated GDDR6 VRAM, supporting 3072 NVIDIA® CUDA® Cores | Màn hình: 16" 2.5K (2560x1600) 500nits, 100% DCI-P3, 240Hz, Acer ComfyView™ LED-backlit, Nvidia Advanced Optimus capable, 16:10 aspect ratio, Wide viewing angle up to 170 degrees | Cổng giao tiếp: 2x USB Type-C™ ports USB Type-C™ port, supporting:   • USB 3.2 Gen 2x2 (up to 20 Gbps)   • DisplayPort over USB-C   • Thunderbolt™ 4   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W   USB Type-C™ port supporting:   • USB 3.2 Gen 2 (up to 10 Gbps)   • DisplayPort over USB-C   • USB charging 5 V; 3 A   • DC-in port 20 V; 65 W  2x USB Standard-A ports, supporting:   • One port for USB 3.2 Gen 2   • One port for USB 3.2 Gen 2 featuring power off USB charging microSD™ Card reader  1x HDMI® 2.1 port with HDCP support  1x DC-in jack for AC adapter  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone | Bàn phím: 3-zone RGB Finger Print trên Touchpad | Audio: DTS X:Ultra Audio | Tản nhiệt: Dual Fan (1x AeroBlade 3D 5th gen), Liquid Metal, Vector heat pipes | Chuẩn LAN: None | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home | Pin: 76Whr Li-ion Battery | Trọng lượng: 2.05 kg | Màu sắc: Sparkly silver | Chất liệu: Cover A, C: Aluminium Cover B, D: Plastic | Kích thước: 356 (W) x 249.17 (D) x 20.83/18.82 (H) mm</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:15</t>
+          <t>2026-07-10 08:03:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>20990000</v>
+        <v>27540000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25490000</v>
+        <v>30300000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 115U (1.50Ghz up to 4.20GHz, 10MB Cache) | VGA: Intel® Graphics | RAM: 16GB (1 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 50WHrs | Trọng lượng: 1.59 kg kg</t>
+          <t>CPU: Intel Core 5 210H (8 lõi / 12 luồng / 2.2 GHz - 4.8 GHz / 12 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / tối đa 32GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (1 khe M.2 2280) | Kích thước màn hình: 16 inch | Pin: 63WHrs 3-cell Li-ion 150W adapter | Trọng lượng: 1.95 kg</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:28</t>
+          <t>2026-07-10 08:03:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus G14 GA403WW QS136WS</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>18890000</v>
+        <v>84990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>23990000</v>
+        <v>89490000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 120U (10 lõi / 12 luồng / 3.8 GHz - 5 GHz / 12 MB Intel Smart Cache) | VGA: Intel® UHD Graphics | RAM: 16GB DDR4 3200MHz (1x 16GB / 2x SO-DIMM / up to 64GB) | SSD: 512GB PCIe NVMe SSD (1x M.2 / up to 2TB) | Kích thước màn hình: 15.6 inch | Pin: 55Wh / 3-cell Li-ion | Trọng lượng: 1.53 kg</t>
+          <t>CPU: AMD Ryzen AI 9 HX 370 | Card đồ họa: NVIDIA GeForce RTX 5080 | Tính chất bề mặt: ASUS | RAM: 64 | SSD: 2TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.57 kg</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g14-ga403ww-qs136ws</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:40</t>
+          <t>2026-07-10 08:03:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20890000</v>
+        <v>53140000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>21990000</v>
+        <v>58460000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen AI 9 465 (10 lõi / 20 luồng / 2.0 GHz - 5.0 GHz / 34 MB Cache) AMD XDNA NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5060 8GB GDDR7 | RAM: 32GB LPDDR5X on board (dual channel / tối đa 32GB) | SSD: 1TB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 14 inch | Pin: 73WHrs 4-cell Li-ion 200W adapter | Trọng lượng: 1.46 kg</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:53</t>
+          <t>2026-07-10 08:03:56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>14890000</v>
+        <v>41260000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17590000</v>
+        <v>45390000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7 14650HX (16 lõi / 24 luồng / 2.2 GHz - 5.2 GHz / 30 MB Cache) | Card đồ họa: NVIDIA GeForce RTX 5050 8GB GDDR7 | RAM: 16GB DDR5 5600MHz SO-DIMM (2 khe / dual channel / tối đa 64GB) | SSD: 512GB PCIe 4.0 NVMe M.2 SSD (2 khe M.2 / nâng cấp tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 70WHrs 4-cell Li-ion | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:08</t>
+          <t>2026-07-10 08:04:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18990000</v>
+        <v>28790000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>19990000</v>
+        <v>30790000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo gaming Gigabyte | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H (2.1 GHz - 4.6 GHz/ 12MB Cache / 8 nhân, 12 luồng) | RAM: 16GB (2x8GB) DDR5 5200MHz (2 khe ram, nâng cấp tối đa 64GB RAM) | Ổ cứng: 512GB PCIe Gen4x4 M.2 SSD (2x PCIe Gen4x4 M.2 slot Up to 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 Laptop GPU 6GB GDDR6 AI TOPs: 321 TOPs | Màn hình: 16.0" WUXGA (1920 x 1200) IPS, 165Hz, 300nits | Cổng giao tiếp: 1 x DC-in 1 x RJ-45 1 x HDMI 2.1 2 x Type-A support USB3.2 Gen1 1x Type-A support USB2.0 1 x Type-C USB3.2 Gen1 support DisplayPort™ 1.4 and Power Delivery 3.0 1x 3.5mm Audio Jack support mic / headphone combo | Bàn phím: Single Color Backlit Keyboard (Green), 1.7mm Key-travel | Chuẩn LAN: 10/100/1000 Mbps | Chuẩn WIFI: WIFI 6E (802.11ax 2x2) | Bluetooth: Bluetooth V5.2 | Audio: 2x 2W speakers Dolby Atmos® | Webcam: HD (720p) Webcam Build-in array Microphone | Hệ điều hành: Windows 11 Home | Pin: Li Polymer 76Wh (up to 12Hrs) | Trọng lượng: ~2.2kg | Màu sắc: Black Steel | Kích thước: 358.3 x 262.5 x 19.45~22.99 mm</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:21</t>
+          <t>2026-07-10 08:04:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-52P-309T (I3-1305U/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VN893SH</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>14390000</v>
+        <v>32190000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>15450000</v>
+        <v>34590000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -938,255 +958,283 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i3 Raptor Lake - 1305U (5 nhân / 6 luồng, 1.6 GHz - 4.5 GHz) | VGA: Intel UHD Graphics | RAM: 8GB (1 x 8GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 3-cell Li-ion, 58 Wh | Trọng lượng: 1.3 kg</t>
+          <t>CPU: AMD Ryzen 3 7335HS | Card đồ họa: AMD Radeon RX 6500M | Tính chất bề mặt: Gigabyte | RAM: 8 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-52p-309t</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:34</t>
+          <t>2026-07-10 08:04:33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 8GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Gigabyte A16 CVHI3VNC93SH</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>22890000</v>
+        <v>33190000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>23990000</v>
+        <v>35590000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 7640HS | Card đồ họa: NVIDIA GeForce RTX 4050 Laptop GPU | Tính chất bề mặt: Gigabyte | RAM: 16 | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 2.2 kg</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vnc93sh</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:46</t>
+          <t>2026-07-10 08:04:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
+          <t>Laptop Gigabyte AERO 16 XE5 73VN938AH</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>23990000</v>
+        <v>42990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24990000</v>
+        <v>82990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 Vali GIGABYTE PISAN LANI | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-12700H 3.6GHz up to 4.9GHz 25MB | RAM: 16GB (8x2) DDR5 4800MHz (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 2TB (2x1TB) Gen4 7K SSD (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 3070 Ti 8GB GDDR6 Boost Clock 1035 MHz / Maximum Graphics Power 105 W | Màn hình: 16" UHD+ (3840x2400) Samsung AMOLED Display (VESA DisplayHDR 500 True Black, 100% DCI-P3) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8125-BG REALTEK (2.5G) Ethernet | Chuẩn WiFi: Intel® AX200 Wireless or Intel® AX201 Wireless (802.11ax, a/b/g/n/ac/ax compatible) wifi 6 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 10 Home | Pin: 4 Cell 99 WHrs | Kích thước: 356 x 248.5 x 22.4 (mm) | Trọng lượng: 2.3 kg</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-aero-16-xe5-73vn938ah</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:59</t>
+          <t>2026-07-10 08:04:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HQVN (I7-13650HX/ RTX 5060 8GB/ 16GB/ 512GB/ 15.3" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>24990000</v>
+        <v>42660000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>25990000</v>
+        <v>44990000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Lenovo Legion Recon Gaming | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) SO-DIMM DDR5 4800MHz (2 slots, nâng cấp tối đa 32GB) | Ổ cứng: 512GB SSD M.2 2242 PCIe® 4.0x4 NVMe® Up to two drives, 2x M.2 SSD • M.2 2242 SSD up to 1TB | Card đồ họa: NVIDIA® GeForce RTX™ 5060 8GB GDDR7, Boost Clock 2497MHz, TGP 115W, 572 AI TOPS | Màn hình: 15.3" WUXGA (1920x1200) IPS 300nits Anti-glare, 100% sRGB, 165Hz, Dolby Vision®, G-SYNC® | Cổng giao tiếp: 2x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-A (USB 5Gbps / USB 3.2 Gen 1), Always On 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with USB PD 65-100W and DisplayPort™ 2.1 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: 24-Zone RGB Backlit, English | Audio: Stereo speakers, 2W x2, audio by HARMAN, optimized with Nahimic Audio | Finger Print: None | Chuẩn LAN: 100/1000M (RJ-45) | Chuẩn WIFI: Wi-Fi® 6, 802.11ax 2x2 | Bluetooth: v5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English, Office Home 2024 + Lenovo® AI Now | Pin: 80Wh, 245W Slim Tip (3-pin) | Trọng lượng: Starting at 1.9 kg (4.19 lbs) | Màu sắc: Eclipse Black | Chất liệu: PC-ABS + 15% Talc (Top), PC-ABS + 15% Talc (Bottom) | Kích thước: 344.9 x 255.35 x 22.50-23.99 mm | Tính năng đặc biệt: AI Chip: LA1</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:11</t>
+          <t>2026-07-10 08:05:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>25990000</v>
+        <v>115990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>26990000</v>
+        <v>117990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 9-275HX (Max Turbo up to 5.4GHz / 36MB / 24 nhân, 24 luồng) Intel AI Boost, up to 13 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 Ti 12GB GDDR7, Boost Clock 2220MHz, TGP 140W, 992 AI TOPS | RAM: 32GB (2 x 16GB) DDR5 6400MHz (2x CSODIMM, tối đa 32GB DDR5-6400) | SSD: 1TB SSD M.2 2242 PCIe 4.0x4 NVMe, tối đa 2TB 1x SSD M.2 NVMe 2280 | Kích thước màn hình: 16 inch | Pin: 80Wh, 400W Slim Tip (3-pin) | Trọng lượng: 2.57 kg</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:23</t>
+          <t>2026-07-10 08:05:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-71P-55P9 (I5-13500H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>17490000</v>
+        <v>30990000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>20490000</v>
+        <v>32990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13500H | VGA: UHD | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 58Wh 3-cell Li-ion battery 90W AC adapter | Trọng lượng: 1.45 kg</t>
+          <t>CPU: AMD Ryzen 7 7735H | Card đồ họa: NVIDIA GeForce RTX 4050 6GB GDDR6 | RAM: 16GB (1 x 16GB) DDR5-4800 SO-DIMM (1x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB SSD M.2 2242 PCIe 4.0x4 | Kích thước màn hình: 15.6 inch | Pin: 3 cell | Trọng lượng: 1.8 kg</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-71p-55p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:36</t>
+          <t>2026-07-10 08:05:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16890000</v>
+        <v>42690000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>18690000</v>
+        <v>45990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core i7-13650HX, 14C (6P + 8E) / 20T, P-core 2.6 / 4.9GHz, E-core 1.9 / 3.6GHz, 24MB | RAM: 16GB (1x16GB) DDR5-4800 SO-DIMM (2x SO-DIMM socket, up to 32GB SDRAM) | Ổ cứng: 512GB  SSD  M.2 2242 PCIe 4.0x4 NVMe (2 Slots: M2 2242 PCIe 4.0 x4 Slot/ M.2 2280 PCIe 4.0 x4 Slot) | Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6, Boost Clock 2370MHz, TGP 105W, 194 AI TOPS | Màn hình: 15.6" FHD (1920x1080) IPS 300nits Anti-glare,  100% sRGB , 144Hz, G-SYNC® | Cổng kết nối: 3x USB-A (USB 5Gbps / USB 3.2 Gen 1) 1x USB-C® (USB 10Gbps / USB 3.2 Gen 2), with PD 140W and DisplayPort™ 1.4 1x HDMI® 2.1, up to 8K/60Hz 1x Headphone / microphone combo jack (3.5mm) 1x Ethernet (RJ-45) 1x Power connector | Bàn phím: White Backlit, English | Audio: High Definition (HD) Audio, Realtek® ALC3287 codec | Chuẩn Lan: 100/1000M | Wifi + Bluetooth: Wi-Fi 6 11ax, 2x2 + BT5.2 | Webcam: HD 720p with E-shutter | Hệ điều hành: Windows® 11 Home Single Language, English | Pin: Integrated 60Wh | Trọng lượng: 2.38 kg | Màu sắc: Luna Grey | Chất liệu: PC-ABS (Top), PC-ABS (Bottom) | Kích thước: 359.6 x 264.8 x 22.1-25.2 mm</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:49</t>
+          <t>2026-07-10 08:05:51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>17990000</v>
+        <v>25190000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>19790000</v>
+        <v>27690000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1195,173 +1243,175 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>CPU: AMD Ryzen 5 7535HS (6 lõi / 12 luồng / 3.3 GHz - 4.55 GHz / 3MB L2 / 16MB L3) | Card đồ họa: NVIDIA GeForce RTX 3050 6GB GDDR6 (TGP 65W) | RAM: 16GB DDR5 4800MHz SO-DIMM (1 x 16GB / 2 khe) | SSD: 512GB SSD M.2 2242 PCIe 4.0 NVMe (2 khe M.2 / tối đa 1TB mỗi ổ) | Kích thước màn hình: 15.6 inch | Pin: 57.5WHrs | Trọng lượng: 1.8 kg</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:02</t>
+          <t>2026-07-10 08:06:04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>19490000</v>
+        <v>33990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>21990000</v>
+        <v>34990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:14</t>
+          <t>2026-07-10 08:06:15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:27</t>
+          <t>2026-07-10 08:06:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>17990000</v>
+        <v>34990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>18990000</v>
+        <v>35990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:39</t>
+          <t>2026-07-10 08:06:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>15990000</v>
+        <v>34890000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>16990000</v>
+        <v>35990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13620H (Turbo Boost up to 4.9 GHz / 24MB / 10 nhân, 16 luồng) | Card đồ họa: Geforce RTX 4050 6GB | RAM: 16GB (2 x 8GB) DDR5 5200MHz (2x SO-DIMM socket, hỗ trợ nâng cấp tối đa 64GB SDRAM) | SSD: 1TB SSD NVMe M.2 PCIe Gen 4 x 4 | Kích thước màn hình: 15.6 inch | Pin: 3 Cell 53.5 Battery (Whr) | Trọng lượng: 2.25 kg</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:51</t>
+          <t>2026-07-10 08:06:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>21990000</v>
+        <v>48490000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>23990000</v>
+        <v>52990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -1370,271 +1420,281 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Gaming MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7 processor 14650HX 16 cores (8 P-cores + 8 E-cores), Max Turbo Frequency 5.2 GHz | RAM: 32GB (2 x 16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB NVMe PCIe Gen 4  SSD  (Total 1 slot M.2-2280 , max 4TB) | VGA: NVIDIA® GeForce RTX™ 5050 Laptop GPU powers advanced AI Up to 2662MHz Boost Clock 115W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 15.6" QHD(2560x1440), 165Hz Refresh Rate,100% DCI-P3(Typical),IPS-Level, 300 nits | Cổng giao tiếp: 1x Type-C (USB3.2 Gen1 / DP) 3x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 1x Mic-in/Headphone-out Combo Jack | Bàn phím: 4-Zone RGB Gaming Keyboard with Copilot Key | Chuẩn LAN: Gigabit Ethernet | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Audio: Nahimic 3 Audio Enhancer Hi-Res Audio Ready 2x 2W Speaker | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 4 cell, 75Whr | Trọng lượng: 2.4 kg | Màu sắc: Đen | Kích thước: 359 x 262 x 25.5 mm</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:04</t>
+          <t>2026-07-10 08:07:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14190000</v>
+        <v>79990000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>16990000</v>
+        <v>80990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5060 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 572 AI TOPS Xung boost tối đa 2497MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:16</t>
+          <t>2026-07-10 08:07:15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>15890000</v>
+        <v>83000000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>16990000</v>
+        <v>85990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 5-5625U (6 lõi / 12 luồng, 2.3 GHz - 4.3 GHz, 16 MB Intel Smart Cache) | VGA: AMD Radeon Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell Li-ion battery Adapter 65W PD Type C | Trọng lượng: 1.45 kg</t>
+          <t>CPU: Intel® Core™ Ultra 9-386H (2.1 GHz - 4.9 GHz / 18MB / 16 nhân, 16 luồng), Intel AI | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Laptop 8GB GDDR7 Sức mạnh tính toán AI mạnh mẽ với 798 AI TOPS Xung boost tối đa 2347MHz, công suất tiêu thụ tối đa 115W với Dynamic Boost. | RAM: 32GB (2 x 16GB) DDR5 (2x SO-DIMM socket, hỗ trợ tối đa 128GB DDR5-7200) | SSD: 1TB NVMe PCIe Gen4 SSD | Kích thước màn hình: 16 inch | Pin: 4 cell / 90 Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:29</t>
+          <t>2026-07-10 08:07:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>18490000</v>
+        <v>67690000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20490000</v>
+        <v>73990000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Stealth Voyage Backpack (kèm máy) | 🎁 MSI Gaming Mouse M99 Pro (kèm máy) | 🎁 Voucher mua hàng trị giá 3,000,000đ | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CPU: AMD Ryzen 7 5825U (8 cores / 16 threads / 2.0 GHz - up to 4.5 GHz / 16MB Cache) | VGA: AMD Radeon Graphics | RAM: 8GB DDR4 3200MHz (1 x 8GB) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 2TB) | Kích thước màn hình: 15.6 inch | Pin: 58Wh / 3-cell Li-ion | Trọng lượng: 1.45 kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 HX 370 Processor with up to 50 NPU TOPS (80 total AI TOPS) | RAM: 32GB LPDDR5x-7500 Onboard ( Không nâng cấp) | Ổ lưu trữ: 1TB NVMe SSD PCIe Gen4 - 1x M.2 SSD slot (NVMe PCIe Gen4) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 Ti Laptop GPU powers advanced AI with 992 AI TOPS Boost Clock 105W Maximum Graphics Power with Dynamic Boost. *May vary by scenario | Màn hình: 16" QHD+(2560x1600) OLED, tỉ lệ 16:10, 240Hz, 100% DCI-P3 (Typ.), VESA DisplayHDR™ 1000 | Cổng giao tiếp: 1x Type-C (USB4® / DisplayPort™/ Power Delivery 3.0/ Thunderbolt™ 4 compatible) 2x Type-A USB3.2 Gen2 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x RJ45 | Bàn phím: Bàn phím chơi game đèn nền RGB Per-Key từ SteelSeries, có phím Copilot | Audio: 2x 2W Audio Speaker 4x 2W Audio Woofer Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: 2.5 Gigabit Ethernet    REALTEK/RTL8125BG-CG | Wifi + Bluetooth: Wi-Fi 7 , Bluetooth v5.4 | Bảo mật: Đầu đọc vân tay Firmware Trusted Platform Module(fTPM) 2.0 Cần gạt che Webcam Khóa Kensington Công nghệ Secured-core PC Công nghệ bảo mật Microsoft Pluton | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 99.9 Whr | Trọng lượng: 2.1 kg | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Màu sắc: Màu Đen (Core Black) | Chất liệu: Magnesium Aluminum | Kích thước: 355.8 x 259.7 x 19.95 mm</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:41</t>
+          <t>2026-07-10 08:07:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0186TX BX9S1PA</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>94990000</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 255HX (20 nhân, 20 luồng, xung tối đa 5.1GHz, 33MB cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 32GB ( 2 x 16) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp tối đa 64GB, dual-channel) | Ổ cứng: 1TB PCIe Gen4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 16:10, 240Hz, VRR, 400 nits, Low Blue Light, viền mỏng, chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung nhôm, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Xbox Game Pass 3 tháng, hỗ trợ Copilot AI, ENERGY STAR® certified | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0186tx-bx9s1pa</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:53</t>
+          <t>2026-07-10 08:07:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>129990000</v>
+        <v>22990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>139000000</v>
+        <v>25290000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:15</t>
+          <t>2026-07-10 08:02:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>109990000</v>
+        <v>24990000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>119000000</v>
+        <v>27990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:30</t>
+          <t>2026-07-10 08:02:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>33990000</v>
+        <v>28990000</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>34990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1644,83 +1704,69 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
+          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:41</t>
+          <t>2026-07-10 08:02:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:58</t>
+          <t>2026-07-10 08:03:07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>28990000</v>
+        <v>26890000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>29990000</v>
+        <v>30990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1730,83 +1776,79 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
+          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:13</t>
+          <t>2026-07-10 08:03:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>25390000</v>
+        <v>49490000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>26990000</v>
+        <v>54990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
+          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:30</t>
+          <t>2026-07-10 08:03:32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>24990000</v>
+        <v>23790000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25990000</v>
+        <v>24490000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1816,36 +1858,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:45</t>
+          <t>2026-07-10 08:03:44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>33900000</v>
+        <v>31490000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>34900000</v>
+        <v>32490000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
@@ -1854,37 +1896,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:59</t>
+          <t>2026-07-10 08:03:56</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>36900000</v>
+        <v>31490000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>37900000</v>
+        <v>32490000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -1893,111 +1935,131 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:11</t>
+          <t>2026-07-10 08:04:09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>44900000</v>
+        <v>43290000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46490000</v>
+        <v>45990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:22</t>
+          <t>2026-07-10 08:04:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>23990000</v>
+        <v>43990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>24990000</v>
+        <v>49490000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:34</t>
+          <t>2026-07-10 08:04:34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>61990000</v>
+        <v>25990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>62990000</v>
+        <v>27990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2006,64 +2068,70 @@
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:46</t>
+          <t>2026-07-10 08:04:49</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>17590000</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:57</t>
+          <t>2026-07-10 08:05:01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>25490000</v>
+        <v>29990000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>25990000</v>
+        <v>30490000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -2079,30 +2147,30 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:09</t>
+          <t>2026-07-10 08:05:15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>22190000</v>
+        <v>34990000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>22690000</v>
+        <v>35990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2111,80 +2179,66 @@
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:20</t>
+          <t>2026-07-10 08:05:27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>20490000</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>22490000</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
+          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:32</t>
+          <t>2026-07-10 08:05:39</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>43990000</v>
+        <v>27890000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>44990000</v>
+        <v>32090000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2195,74 +2249,78 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:46</t>
+          <t>2026-07-10 08:05:51</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>33990000</v>
+        <v>7390000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>34990000</v>
+        <v>12950000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-43%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
+          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:57</t>
+          <t>2026-07-10 08:06:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>32990000</v>
+        <v>23490000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>39990000</v>
+        <v>24290000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2272,482 +2330,532 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:09</t>
+          <t>2026-07-10 08:06:15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>37990000</v>
+        <v>25890000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>39990000</v>
+        <v>26990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G502 Hero Gaming (trị giá 920.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
+          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:21</t>
+          <t>2026-07-10 08:06:31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46990000</v>
+        <v>23490000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>48990000</v>
+        <v>26490000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G502 Hero Gaming (trị giá 920.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
+          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:33</t>
+          <t>2026-07-10 08:06:44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
+        <v>25990000</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G502 Hero Gaming (trị giá 920.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:45</t>
+          <t>2026-07-10 08:06:57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
+        <v>25790000</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>29090000</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G502 Hero Gaming (trị giá 920.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:56</t>
+          <t>2026-07-10 08:07:09</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>82990000</v>
+        <v>28990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>83990000</v>
+        <v>33990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột Logitech G502 Hero Gaming (trị giá 920.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:08</t>
+          <t>2026-07-10 08:07:22</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>86990000</v>
+        <v>48790000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>87990000</v>
+        <v>50990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
+          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:20</t>
+          <t>2026-07-10 08:07:34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>22990000</v>
+        <v>59490000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>25290000</v>
+        <v>64390000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Màn hình Acer KG240Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ 5 Processor 120U 1.4 GHz (12MB Cache, up to 5.0 GHz, 10 cores, 12 Threads) | VGA: Intel® UHD Graphics | RAM: 8GB (1x8GB) DDR4 3200MHz (2x SO-DIMM socket, up to 32GB SDRAM) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 58Wh 3-cell | Trọng lượng: 1.6 kg kg</t>
+          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:09</t>
+          <t>2026-07-10 08:07:47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>24990000</v>
+        <v>43890000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>27990000</v>
+        <v>50590000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000₫) | [Laptop] Tặng kèm Chuột Logitech M331 khi mua Laptop Acer Aspire Go hay Lite | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5-125H (18M Cache, up to 4.50 GHz, 14 cores 18 threads) | VGA: Intel® Arc™ Graphics | RAM: 16GB LPDDR5X (không nâng cấp được) | SSD: 512GB | Kích thước màn hình: 16 inch | Trọng lượng: 1.6 kg</t>
+          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:27</t>
+          <t>2026-07-10 08:07:59</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>28990000</v>
+        <v>24390000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>34990000</v>
+        <v>28190000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 Processor 226V 16GB 1.6 GHz (8MB Cache, up to 4.5 GHz, 8 cores, 8 Threads); Intel® AI Boost NPU up to 40 TOPS | RAM: 16GB LPDDR5 8533 MT/s Onboard | Ổ cứng: 1TB NVMe PCIe Gen 4 SSD chuẩn EVO (1 khe SSD, Hỗ trợ nâng cấp tối đa 2TB) | Card đồ họa: Intel® Arc™ Graphics 130V | Màn hình: 14" 3K (2880 x 1800) OLED SlimBezel, HDR 550 nits (400 native), DCI-P3 100% / Adobe100%, 90Hz | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x Headphone/speaker jack | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wi-Fi 7 Wireless LAN | Bluetooth: v5.4 | Webcam: 1440p QHD video at 30 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.26 kg | Pin: 3 Cell 65Whrs | Màu sắc: Steam Blue | Chất liệu: Cover A, C, D: Aluminum  Cover B: ABS Plastic | Kích thước: 312.4 (W) x 221.2 (D) x 9.7/15.95 (H) mm</t>
+          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:40</t>
+          <t>2026-07-10 08:08:12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
+        <v>129990000</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, hỗ trợ NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5090 Laptop GPU (24GB GDDR7, hỗ trợ DLSS 4, Ray Tracing, Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size, đèn RGB Per-Key, tích hợp phím số, công nghệ NKRO Anti-Ghosting, khung phím RGB, có phím Copilot AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Microsoft Office Home 2024 + Microsoft 365 Basic, Otter.ai, McAfee 30 ngày, Copilot in Windows, Xbox Game Pass 3 tháng | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0212tx-c1wr1pa</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:13:53</t>
+          <t>2026-07-10 08:02:23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Gaming OMEN MAX 16 ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>26890000</v>
+        <v>109990000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>30990000</v>
+        <v>119000000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer Office | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây</t>
+          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 226V | VGA: Intel Arc | RAM: 16 | SSD: 512GB | Kích thước màn hình: 14 inch</t>
+          <t>CPU: Intel® Core™ Ultra 9 275HX (24 nhân, 24 luồng, xung tối đa 5.4GHz, 36MB L3 cache, tích hợp NPU AI Boost 13 TOPS) | RAM: 64GB (2 x 32GB) DDR5 5600MHz (2 khe SO-DIMM, hỗ trợ nâng cấp, dual-channel) | Ổ cứng: 2TB PCIe Gen 4 NVMe M.2 SSD ( 2 slot SSD 2280) | Card đồ họa: NVIDIA® GeForce RTX™ 5080 Laptop GPU (16GB GDDR7, DLSS 4, Ray Tracing, hỗ trợ Advanced Optimus) | Màn hình: 16.0-inch OLED UWVA 2.5K (2560 x 1600), 240Hz, VRR, 400 nits, 100% sRGB, Low Blue Light, thời gian phản hồi nhanh, viền mỏng chống chói | Cổng kết nối: 1 x HDMI 2.1, 1 x RJ-45 LAN, 1 x USB-A 10Gbps, 1 x combo audio 3.5mm 2 x Thunderbolt™ 4 (USB-C 40Gbps, DP 2.1, PD, Sleep &amp; Charge), 1 x USB-A 10Gbps, 1 x AC Smart Pin | Bàn phím: Full-size RGB Per-Key, có phím số, khung phím RGB, hỗ trợ Copilot Windows AI | Audio: Dual speakers, DTS:X® Ultra, HP Audio Boost, HyperX tuning | Chuẩn Lan: RJ-45 10/100/1000/2500 Mbps | Wifi + Bluetooth: Intel® Wi-Fi 6E AX211 (2x2) and Bluetooth® 5.3 wireless card (supporting gigabit data rate) | Webcam: HP True Vision 1080p FHD IR camera, hỗ trợ Windows Hello, có màn che camera | Hệ điều hành: Windows 11 Home Single Language, bản quyền tích hợp Windows 11 Home + Microsoft Office Home 2024 + Microsoft 365 Basic | Pin + Sạc: 6-cell Li-ion polymer, 83WHrs, sạc nhanh 50% trong 30 phút, 330W AC Adapter | Trọng lượng: 6.1 lbs (khoảng 2.77 kg) | Màu sắc + Chất liệu: Shadow Black, vỏ nhôm nguyên khối, có thanh đèn light bar | Kích thước: 14.04 x 10.59 x 0.90 ~ 0.98 inch</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-omen-max-16-ah0213tx-c1wr2pa</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:05</t>
+          <t>2026-07-10 08:02:38</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 14 OLED 9MF E2VNBB4SH</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>49490000</v>
+        <v>33990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>54990000</v>
+        <v>34990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra X7 Processor 358H (18MB Cache, up to 4.8 GHz, 16 Cores, 16 Threads) 50 TOPS | VGA: Intel® Arc™ B390 GPU (đồ họa tích hợp) | RAM: 32GB LPDDR5X 9600Mhz (không nâng cấp được) | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 71 Wh (Lithium Ion) | Trọng lượng: 1.12 kg</t>
+          <t>CPU: Intel Core i5-12500H ( 2.5 GHz - 4.5 GHz / 18MB / 12 Cores, 16 Threads ) | RAM: 16GB LPDDR5 4800MHz (Onboard không nâng cấp) | Ổ cứng: 1TB M.2 PCIe Gen 4 x 4 (2 Slots) | Card màn hình: NVIDIA® GeForce RTX™ 4050 6GB | Màn hình: 14.0" Thin Bezel 2.8K QHD+ 2880x1800 OLED 16:10 Display (VESA DisplayHDR 600 True Black, 100% DCI-P3, 90Hz, TÜV Rheinland-certified, Eyesafe® 2.0) | Bàn phím: Backlit Keyboard (Single Color, white) | Âm thanh: DTS : X Ultra | Chuẩn WiFi: WiFi 802.11ax (Wifi 6) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD  1x USB 3.2 Gen1 (Type-A)  1x MicroSD Card Reader 1x 3.5mm Audio Combo 1x HDMI 2.1  1x DC-in | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Pin: 63 WHrs | Kích thước: 311 x 220.8 x 17 (mm) | Trọng lượng: 1.49 kg</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-14-oled-9mf-e2vnbb4sh</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:17</t>
+          <t>2026-07-10 08:02:50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-73-57FZ (Ultra 5-125H/ 16GB/ 512GB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Gigabyte Aero 17 XE5 73VN744AH</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>23790000</v>
+        <v>38990000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>24490000</v>
+        <v>39990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
@@ -2761,36 +2869,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 125H (upto 4.5GHz, 14 lõi 18 luồng, 18 MB Intel® Smart Cache) | RAM: 16GB (1x16GB) LPDDR5 6400MHz Onboard (Không nâng cấp được) | Ổ cứng: 512GB PCIe NVMe SED SSD (2 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics | Màn hình: 14" 2.8K (2880x1800) OLED 16:10 aspect ratio, 90Hz, 400nits, DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™    port supporting:  • USB4® 40Gbps  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard-A ports, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 1 featuring power off USB charging 1x microSD™ Card reader 1x Headphone/speaker jack 1x HDMI® 1x 2.1 port with HDCP support | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.32kg | Pin: 65 Whr 4-cell | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D: Aluminum | Kích thước: 312.9 (W) x 217.9 (D) x 14.9 (H) mm</t>
+          <t>CPU: Intel Core i7-12700H (Up to 4.7GHz) 14 Cores 20 Threads | RAM: 32GB (2x16GB) DDR5 4800MHz (upto 64GB) | Ổ cứng: 1TB SSD M.2 2280 PCIe NVMe Gen4 x4 (Còn trống 1 Slot SSD M.2 2280 PCIe NVMe) | Card màn hình: NVIDIA GeForce RTX 3070 Ti Laptop GPU 8GB GDDR6 | Màn hình: 17.3" Thin Bezel UHD (3840x2160) IPS-level miniLED, VESA DisplayHDR 1000, 120Hz Refresh Rate | Bàn phím: GIGABYTE Fusion RGB Per-Key Backlit | Âm thanh: 2 x 2 Watt Speaker Microphone DTS:X® Ultra | Chuẩn WiFi: Intel WiFi 6E AX210 (802.11ax, a/b/g/n/ac/ax) | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 2x Thunderbolt™ 4 Support DP / one port support PD in 100W 1x USB 3.2 Gen2 (Type-C) Support DP 1x 3.5mm Audio Combo 1x DC-in Jack | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 4 Cell 99WHrs | Kích thước: 396.2 x 241.3 x 23.4 mm | Trọng lượng: 2.6 kg</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-sfg14-73-57fz</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-17-xe5-73vn744ah</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:29</t>
+          <t>2026-07-10 08:03:08</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Gigabyte G5 KC 5S11130SH</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>31490000</v>
+        <v>28990000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>32490000</v>
+        <v>29990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -2802,38 +2910,42 @@
           <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Nhà sản xuất | : GIGABYTE | Xuất xứ | : Chính hãng | Bảo hành | : 24 tháng | Tình trạng | : Mới 100% | Khuyến mãi: | Ưu đãi đặc biệt khi mua kèm LAPTOP: | Mua kèm màn hình giảm sốc lên đên 49% ( | xem chi tiết | ). | Mua kèm các sản phẩm khác giảm giá lên đến 56% ( | xem chi tiết | ). | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON.</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core Ultra 5 225H | VGA: Intel Arc | RAM: 16 | SSD: 1TB | Kích thước màn hình: 14 inch | Trọng lượng: 1.28kg kg</t>
+          <t>CPU: Intel Core i5-10500H | VGA: RTX 3060 | SSD: 512GB | Kích thước màn hình: 15.6 inch</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-g5-kc-5s11130sh</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:41</t>
+          <t>2026-07-10 08:03:23</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop GIGABYTE U4 UD 70S1823SO</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>31490000</v>
+        <v>25390000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>32490000</v>
+        <v>26990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2843,40 +2955,40 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo Acer Office | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>Thông tin chung: | Nhà sản xuất: | GIGABYTE | Xuất xứ: | Chính hãng | Bảo hành: | 24 Tháng | Tình trạng: | Mới | 🎁 Giảm ngay 200.000đ khi mua chuột Logitech G203 kèm Laptop Gaming (Từ 01/06 - 30/06/2022) | ƯU ĐÃI KHI MUA KÈM LAPTOP: | ⭐ Mua chuột không dây LM115G Wireless chỉ với 100,000đ. | ⭐ Giảm ngay 100,000đ khi mua thêm màn hình máy tính. | ⭐ Giảm ngay 100,000đ khi mua thêm Ram. | ⭐ Giảm ngay 100,000đ khi mua kèm Microsoft Office (01/10 - 31/12/2022) | Và còn rất nhiều ưu đãi khác. | XEM NGAY CHI TIẾT TẠI ĐÂY | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 5 processor 225H (upto 4.9GHz, 14 lõi 14 luồng, 18 MB Intel® Smart Cache) NPU Peak TOPS : 13 TOPS | RAM: 16GB  LPDDR5 7500MHz Onboard (Không nâng cấp được) | Ổ cứng: 1TB PCIe NVMe SSD (1 slots, nâng cấp tối đa 2TB) | Card đồ họa: Intel® ARC™ Graphics GPU Peak TOPS (Int8) : 63 TOPS | Màn hình: 14" FHD+ IPS Screentouch FHD+ (1920x1200) 16:10 aspect ratio, 60Hz, 400nits, sRGB 100% | Cổng giao tiếp: USB Type-C 2x USB Type-C™ ports USB Type-C™ port supporting: • USB4® 40Gbps • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 100 W USB Standard A 2x USB Standard-A ports, supporting: • 1x port for USB 3.2 Gen 1 • 1x port for USB 3.2 Gen 1 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x Headphone/speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, Đơn sắc - Trắng | Bảo mật: Power keycap fingerprint reader with on-chip matching design | Chuẩn WIFI: Killer Wi-Fi 7 Wireless LAN  • 802.11 a/b/g/n/ac/ax/be  • Band: 2.4 GHz, 5 GHz, and 6 GHz  • 2x2 MIMO technology | Bluetooth: v5.3 | Webcam: 2560 x 1440 resolution 1440p QHD video at 30 fps with Temporal | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.28kg | Pin: 65 Wh 4-cell Li-ion battery Supports Fast Charging technology 100W Type-C adapter | Màu sắc: Pure Silver | Chất liệu: Cover A/C/D : Aluminum  Icon/Logo : Aluminum  Cover bản lề/Inner : Plastic  Touchpad : Glass | Kích thước: 312.4 (W) x 221.2 (D) x 9.6/16.4 (H) mm</t>
+          <t>CPU: Intel Core i7-1195G7 (4 lõi, 8 luồng, tối đa 5,0 GHz) | RAM: 16GB (8GB onboard + 1 khe 8GB) DDR4-3200Mhz | Ổ cứng: 512GB SSD M.2 2242 PCIe NVMe 3.0x4, 1 slot nâng cấp | Card màn hình: Intel Iris Xe graphics | Màn hình: Màn hình LCD 14 inch FHD (1920x1080) IPS chống chói ~ 100% sRGB | Bàn phím: Bàn phím tiêu chuẩn | Âm thanh: DTS : X Ultra | Chuẩn LAN: RTL8411B REALTEK (1G) Ethernet | Chuẩn WiFi: Intel AX201 Wireless (802.11ax, a/b/g/n/ac/ax) + Bluetooth 5.2 | Bluetooth: Bluetooth® V5.2 | Cổng kết nối: 1 x USB 3.2 Gen2 Loại-A 1 x USB 3.2 Gen1 Type-A 1 x ThunderBolt 4 1 x HDMI 2.0 1 x kết hợp âm thanh 1 x đầu đọc thẻ MicroSD 1 x DC-in | Webcam: HD Camera | Hệ điều hành: Windows 11 Home | Pin: 36Wh | Kích thước (W x D x H): 322 x 216.8 x 17.2 mm | Trọng lượng: 990g</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-u4-ud-70s1823so</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:14:54</t>
+          <t>2026-07-10 08:03:38</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" WQXGA+/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 6 14IRH8 83E0000VVN</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>43290000</v>
+        <v>24990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>45990000</v>
+        <v>25990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2886,83 +2998,79 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Quà tặng: | 🎁 Balo SUV Acer | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 36 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i7-13700H 3.70 upto 5.00GHz ,14 Core 20 Threads, 24 MB Smart Cache | RAM: 32GB LPDDR5 Onboard | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ Graphics 4050 6GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2 x USB Type-C Port (Supporting DisplayPort over USB-C, ThunderBolt 4, USB Charging 5V; 3A) 2 x USB Standard A Port 1 x HDMI@ 2.1 port with HDCP support 1 x MicroSD reader 1 x 3.5mm Headphone//Speaker jack | Audio: Acer TrueHarmony technology | Bàn phím: Có LED, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i | Bluetooth: v5.1 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A: nhôm Cover B: nhựa Cover C: nhôm Cover D: nhôm | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel Core i7-13700H | VGA: Intel Iris Xe Graphics | SSD: 512GB | Kích thước màn hình: 14 inch</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-6-14irh8-83e0000vvn</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:06</t>
+          <t>2026-07-10 08:03:53</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>43990000</v>
+        <v>33900000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>49490000</v>
+        <v>34900000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Quà tặng: | 🎁 Balo Acer SUV | 🎁 | Tốt nghiệp rồi - Nhận quà thôi (Từ 17.7 - 31.10.2024) | - 1 thẻ nạp Game VNG 500.000 VNĐ hoặc 1 thẻ mua sắm Got It 200.000 VNĐ tùy bạn chọn. | - 1 cơ hội trúng vali Acer Predator trị giá 8.000.000 VNĐ (quà tặng đặc biệt dành cho 4 khách hàng đăng ký thông tin hợp lệ sớm nhất mỗi thứ 2 hàng tuần). | 🎁 | Voucher ưu đãi Học sinh - Sinh viên trị giá 300k (Từ 01.08 - 31.10.2024) | ✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ Ultra 7 155H, 1.40 GHz upto 4.80 GHz, 16 nhân 22 luồng, 24MB Intel® Smart Cache | RAM: 32GB LPDDR5 Onboard 6400Mhz | Ổ cứng: 1TB PCIe NVMe SED SSD (Không nâng cấp được) | Card đồ họa: NVIDIA® GeForce RTX™ 4060 with 8 GB GDDR6 | Màn hình: 14.5" 2.8K WQXGA+ (2880x1800) OLED, 120Hz, 400 nits. DCI-P3 100%, Adobe100% | Cổng giao tiếp: 2x USB Type-C™, supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • Thunderbolt™ 4  • USB charging 5 V; 3 A  • DC-in port 20 V; 100 W 2x USB Standard A, supporting:  • One port for USB 3.2 Gen 1  • One port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in  microphone" | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Có LED trắng, bảo mật vân tay | Bảo mật: Firmware Trusted Platform Module (TPM) solution  BIOS user, supervisor passwords | Chuẩn WIFI: Killer™ Wireless Wi-Fi 6E 1675i  (802.11 a/b/g/n/ac/ax wireless LAN) | Bluetooth: v5.3 | Webcam: FHD Camera | Hệ điều hành: Windows 11 Home Single Language | Trọng lượng: 1.5kg | Pin: 76Whr Li-ion battery | Kích thước: 322.79 (W) x 228.12 (D) x 17.9 (H) mm | Chất liệu: Cover A/C/D: Aluminum  Cover B: Plastic | Màu sắc: Steel Gray</t>
+          <t>CPU: Intel Core Ultra 5 325 (8 nhân (4 P-cores + 4 E-cores) / 8 luồng / 4.5 GHz / 12MB Cache) | VGA: Intel Graphics | RAM: 16GB LPDDR5X 7500MHz on board | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 72Wh | Trọng lượng: 1.12 kg</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:20</t>
+          <t>2026-07-10 08:04:08</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>25990000</v>
+        <v>36900000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>27990000</v>
+        <v>37900000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2971,74 +3079,68 @@
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ 5 Processor 210H (2.7 GHz up to 5.0 GHz, 24MB Cache, 10 nhân, 12 luồng) | VGA: Intel® UHD Graphics | RAM: RAM 16GB DDR5 SO-DIMM | SSD: 512GB | Kích thước màn hình: 14 inch | Pin: 50WHrs, 3S1P, 3-cell Li-ion | Trọng lượng: 1.4 kg</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:38</t>
+          <t>2026-07-10 08:04:20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-I516-50W (I5-13420H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>17590000</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr"/>
+        <v>44900000</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46490000</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi chống shock GearVN 14 inch | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ i5-13420H Processor 2.1 GHz (12MB Cache, up to 4.6 GHz, 8 cores, 12 Threads) | RAM: 16GB (16GBx1) DDR5 (2x SO-DIMM socket, up to 64GB SDRAM) | Ổ cứng: 512GB M.2 2280 NVMe™ PCIe® 4.0 SSD | VGA: Intel® UHD Graphics | Màn hình: 14.0 FHD (1920 x 1080) 16:9, IPS-level, 60Hz, LED Backlit, Anti-glare display, NTSC: 45%, View angle 170, Screen-to-body ratio 87% | Cổng giao tiếp: 2x USB 3.2 Gen 1 Type-A 2x USB 3.2 Gen 2 Type-C support display / power delivery 1x HDMI 1.4 1x 3.5mm Combo Audio Jack 1x RJ45 Gigabit Ethernet FingerPrint | Bàn phím: Bàn phím dạng Chiclet, Hành trình phím 1,35 mm, Bàn phím chống tràn Đèn bàn phím: Không | Audio: Audio by Dirac Built-in speaker Built-in array microphone | Bảo mật: Bảo mật và Bảo vệ mật khẩu người dùng HDD Bảo vệ BIOS bằng mật khẩu Trusted Platform Module (TPM) 2.0 Thiết lập mật khẩu người dùng BIOS Hỗ trợ Absolute Persistence 2.0 (Computrace) Cảm biến vân tay tích hợp với chuột cảm ứng Khóa Kensington Nano Security Slot™(6x 2.5mm) | Chuẩn LAN: None | Chuẩn WIFI: Wi-Fi 6(802.11ax) (Băng tần kép) 2*2 | Bluetooth: Bluetooth® 5.3 Wireless Card | Webcam: 720p HD camera ; With privacy shutter | Hệ điều hành: Windows 11 Home | Pin: 3 Cell 50WHrs | Trọng lượng: 1.41 kg | Màu sắc: Misty Grey | Chất liệu: LCD cover (Plastic), Top case (Plastic) | Kích thước: 32.45 x 21.44 x 1.97 ~ 1.97 cm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-i516-50w</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:15:50</t>
+          <t>2026-07-10 08:04:32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" IPS/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>29990000</v>
+        <v>23990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>30490000</v>
+        <v>24990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3047,33 +3149,37 @@
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel Core Ultra 5 115U (8 nhân (2 P-cores + 4 E-cores + 2 LPE-cores) / 10 luồng / 4.2 GHz / 10MB Cache) | VGA: Intel Graphics | RAM: 16GB DDR5 5600MHz on board | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 51Wh | Trọng lượng: 1.7 kg</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:03</t>
+          <t>2026-07-10 08:04:44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>34990000</v>
+        <v>61990000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>35990000</v>
+        <v>62990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3085,63 +3191,65 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:15</t>
+          <t>2026-07-10 08:04:56</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>199990000</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
+        <v>36990000</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel® Core™ Ultra 9 Processor 386H 2.1 GHz (18MB Cache / up to 4.9 GHz / 16 cores / 16 Threads) Intel® NPU up to 50TOPS | Card đồ họa: NVIDIA GeForce RTX 5090 24GB GDDR7 | RAM: 64GB LPDDR5X 8533 on board | SSD: 2TB PCIe 5.0 NVMe M.2 Performance SSD (2 khe M.2 / tối đa 2TB) | Kích thước màn hình: 16 inch | Pin: 90WHrs / 4S1P / 4-cell Li-ion | Trọng lượng: 2.82 kg</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:27</t>
+          <t>2026-07-10 08:05:07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406KA PP113WS</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>27890000</v>
+        <v>25490000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>32090000</v>
+        <v>25990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3150,80 +3258,72 @@
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>CPU: Intel Core Ultra 7 155H | VGA: Intel Arc | SSD: 512GB | Kích thước màn hình: 14 inch</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ka-pp113ws</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:40</t>
+          <t>2026-07-10 08:05:19</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Avita PURA A+ AF14A3VNF56F Silver</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>7390000</v>
+        <v>22190000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>12950000</v>
+        <v>22690000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-43%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Đổi mới trong vòng 7 ngày đầu ( Lỗi do nhà sản xuất) | ✔ Hỗ trợ đổi mới trong | 90 ngày. | (Lỗi do nhà sản xuất) | ✔ Miễn phí giao hàng toàn quốc. | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1235U | VGA: Onboard | RAM: 8GB DDR4 3200MHz | SSD: 512GB | Kích thước màn hình: 14 inch | Trọng lượng: 1.3 kg</t>
+          <t>CPU: Intel Core 5 120U (10 lõi (2 P-cores + 8 E-cores) / 12 luồng / 5.0 GHz) | VGA: Intel UHD Graphics | RAM: 16GB DDR4 3200MHz (up to 64GB) | SSD: 512GB | Kích thước màn hình: 15.6 inch | Pin: 3-Cell (46.8 Whrs) | Trọng lượng: 1.7 kg</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-avita-pura-a-af14a3vnf56f-silver</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:16:51</t>
+          <t>2026-07-10 08:05:31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Inspiron 5430 N4I5497W1 Silver</t>
+          <t>Laptop MSI Modern 15 H AI C2HMG 220VN</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>23490000</v>
+        <v>20490000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>24290000</v>
+        <v>22490000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3233,200 +3333,204 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 12 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ). | Gợi ý laptop giá tốt hiệu năng cao: | Laptop ASUS Vivobook 14 OLED A1405VA KM095W</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Túi MSI ( kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON | ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-1335U upto 4.60GHz, 10 cores 12 threads, 12MB Cache | RAM: 16GB LPDDR5 4800MHz Onboard | Ổ cứng: 512GB  SSD  M.2 PCIE | Card đồ họa: Intel Iris Xe Graphics (Khi chạy Dual Ram) Intel UHD Graphics | Màn hình: 14 inch FHD 60Hz, AG, Wide Viewing Angle, 250 nits, ComfortView | Cổng giao tiếp: 2 USB 3.2 Gen 1 Type-A ports 1 Thunderbolt 4 port with DisplayPort and Power Delivery 1 Audio jack 1 HDMI 1.4 port (Maximum resolution supported over HDMI is 1920x1080 @60Hz. No 4K/2K output) 1 Power-adapter port | Bàn phím: Có đèn bàn phím | Bảo mật: Có bảo mật vân tay | Wireless + Bluetooth: Intel Wi-Fi 6E (6GHz) AX211 2x2 Bluetooth 5.2 | Đọc thẻ nhớ: 1 SD-card slot | Audio: Stereo speakers with Waves MaxxAudio Pro, 2 W x 2 = 4 W | Webcam: 1080p at 30 fps FHD camera Dual-array microphones | Pin: 4-cell Li-ion, 54 Wh | Hệ điều hành: Windows 11 Home SL + Office Home &amp; Student 2021 | Kích thước: 314.00 x 226.6 x 15.74 - 17.67mm | Trọng lượng: 1.53 kg | Màu sắc: Silver</t>
+          <t>CPU: Intel® Core™ Ultra 7 processor 255H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), 16 thread, 24MB cache, Max Turbo Frequency 5.1 GHz | RAM: 16GB (8x2) DDR5 5600MHz ( 2 slot, tối đa 96 MB) | Ổ cứng: 512 GB NVMe SSD PCIe Gen4 ( Tổng 1 slot, max 4TB) | Card đồ họa: Intel® Iris Xe Graphics | Màn hình: 15.6inch FHD IPS, 60Hz, 45% NTSC | Cổng giao tiếp: 1x Type-C (USB3.2 Gen2 / DisplayPort™/ Power Delivery 3.0) 3x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (4K @ 60Hz) 1x microSD Card Reader 1x Mic-in/Headphone-out Combo Jack | Audio: 2x 2W Speaker Hi-Res Audio Ready | Bàn phím: Single Backlit Keyboard (White) with Copilot Key | Chuẩn WIFI: Intel® Wi-Fi 6E AX211 | Bluetooth: v5.3 | Webcam: HD type (30fps@720p) | Hệ điều hành: Windows 11 Home (MSI recommends Windows 11 Pro for business.) | Pin: 3-Cell,39.3 Whrs | Chất liệu: A Side : Metal B/C/D side : Plastic | Trọng lượng: 1.6kg | Màu sắc: Black | Kích thước: 359 x 241 x 19.6 mm</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-inspiron-5430-n4i5497w1-silver</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-h-ai-c2hmg-220vn</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:04</t>
+          <t>2026-07-10 08:05:43</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53GZ (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>25890000</v>
+        <v>43990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>26990000</v>
+        <v>44990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 5-210H (8 lõi / 12 luồng, 2.2 GHz - 4.8 GHz, 12 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (nâng cấp tối đa 4TB SSD) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel Core Ultra 7 355 | VGA: Intel Arc Graphics | RAM: 32GB LPDDR5X on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:20</t>
+          <t>2026-07-10 08:05:55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-55MD (I5-13420H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>23490000</v>
+        <v>33990000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>26490000</v>
+        <v>34990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H 8 nhân 16 luồng, Up to 4.6 Ghz 12 MB Intel® Smart Cache | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Tính chất bề mặt: Acer | RAM: 16GB (16x1) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (2 slot, support M.2 2280 PCIe 4.0x4)- Max 4 TB | Kích thước màn hình: 15.6 inch | Pin: 3 Cell, 54.8Whr | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core 7 350 | VGA: Intel Arc Graphics | RAM: 16GB LPDDR5x on board | SSD: 1TB | Kích thước màn hình: 16 inch | Pin: 4-cell 81Wh | Trọng lượng: 1.59 kg</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-55md</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:32</t>
+          <t>2026-07-10 08:06:07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>25990000</v>
+        <v>32990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>29990000</v>
+        <v>39990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Windows bản quyền tích hợp. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Chuột MSI M98 (kèm máy) | 🎁 Túi Topload (kèm máy) | ⭐ | Ưu đãi lên đến 54% khi mua kèm Laptop | xem ngay tại đây | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>CPU: Intel® Core™ Ultra 7 processor 155H with Intel® AI Boost (NPU) 16 cores (6 P-cores + 8 E-cores + 2 Low Power E-cores), Max Turbo Frequency 4.8 GHz | RAM: 32GB LPDDR5 6400MHz (không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD  (1 x slots M.2 NVMe PCIe Gen4) | Card đồ họa: Intel® Arc™ graphics (Intel® Arc™ graphics requires configuration with 16GB dual-channel memory or above) | Màn hình: 13.3" 2.8K (2880 x 1800), OLED, VESA DisplayHDR™ 500 Certified, 100% DCI-P3 (Typical) | Cổng giao tiếp: 2x Type-C (USB / DP / Thunderbolt™ 4) with PD charging 1x Type-A USB3.2 Gen1 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) 1x Micro SD 1x Mic-in/Headphone-out Combo Jack | Bàn phím: Single Backlit Keyboard (White) | Audio: 2x 2W Audio Speaker Hi-Res Audio Ready, DTS Audio Processing Spatial Array Microphone (3 Mic) | LAN: None | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750, Bluetooth v5.4 | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Bảo mật: Fingerprint Security Discrete Trusted Platform Module (dTPM) 2.0 Firmware Trusted Platform Module (fTPM) 2.0 Webcam Shutter, Kensington Lock | Pin: 4-Cell 75 Whrs | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Kích thước: 299 x 210 x 16.9 mm</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:45</t>
+          <t>2026-07-10 08:06:19</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-78WG (I7-13620H/ RTX 3050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>25790000</v>
+        <v>37990000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>29090000</v>
+        <v>39990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Tặng ngay 1 x Chuột Logitech G102 LightSync Black (trị giá 400.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm ngay 100.000đ khi mua Microsoft Office kèm laptop. | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | QUÀ TẶNG: | 🎁 | Balo Acer Predator SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
+          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 MSI Topload Bag (kèm máy) | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core i7-13620H (10 lõi / 16 luồng, 3.6 GHz - 4.9 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 VRAM, hỗ trợ 2560 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion, 150W adapter | Trọng lượng: 1.99 kg</t>
+          <t>CPU: Intel Core™ Ultra 7 258V up to 4.80Ghz, 8 Cores (4P+4PLE), 8 Threads, 12MB Intel® Smart Cache | RAM: 32GB Onboard 8533MHz LPDDR5x (Không nâng cấp) | Ổ lưu trữ: 1TB NVMe PCIe Gen4x4 SSD (1 x M.2 SSD slots) | Card đồ họa: Intel® Arc™ 140V | Màn hình: 13.3" 2.8K (2880x1800), OLED, đạt chuẩn VESA DisplayHDR™ 500, 100% DCI-P3 (Typ.) | Cổng giao tiếp: 2x Thunderbolt™ 4 (DisplayPort™/ Power Delivery 3.0) 1x Type-A USB3.2 Gen1 1x Đầu đọc thẻ Micro SD 1x HDMI™ 2.1 (8K @ 60Hz / 4K @ 120Hz) | Bàn phím: Bàn phím đèn nền đơn sắc (trắng), có phím Copilot | Audio: 2x 2W Audio Speaker Sound by Dynaudio, Nahimic 3 Audio Enhancer, Hi-Res Audio Ready | LAN: Gb LAN | Wifi + Bluetooth: Intel® Killer™ Wi-Fi 7 BE1750(s) + Bluetooth v5.4 | Bảo mật: Discrete Trusted Platform Module(dTPM) 2.0 Firmware Trusted Platform Module(fTPM) 2.0 Webcam Shutter, Kensington Lock, Microsoft Pluton Security Technology | Webcam: IR FHD type (30fps@1080p) with HDR 3D Noise Reduction+ (3DNR+) | Pin: 4 cell / 75 Whr | Trọng lượng: 0.99 kg | Hệ điều hành: Windows 11 Home | Màu sắc: Stellar Gray | Chất liệu: Magnesium Aluminum | Kích thước: 299 x 210 x 16.9 mm</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:17:57</t>
+          <t>2026-07-10 08:06:31</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-79XF (Core 7-240H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>28990000</v>
+        <v>46990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>33990000</v>
+        <v>48990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3437,242 +3541,206 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel Core 7-240H (10 lõi / 16 luồng, 1.8 GHz - 5.2 GHz, 24 MB Intel Smart Cache) | Card đồ họa: NVIDIA GeForce RTX 3050 6 GB GDDR6 2560 NVIDIA CUDA Cores | RAM: 16GB (1x16GB) DDR4 3200MHz (2x SO-DIMM socket, up to 64GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Nâng cấp tối đa 4TB) | Kích thước màn hình: 15.6 inch | Pin: 54.8Wh 4-cell Li-ion battery 150W adapter | Trọng lượng: 2.07 kg</t>
+          <t>CPU: Intel® Core™ Ultra 7-355 (2.3 GHz - 4.7 GHz / 12MB / 8 nhân, 8 luồng), Intel AI | VGA: Intel® Arc™ graphics | RAM: 32GB LPDDR5x Onboard | SSD: 1TB | Kích thước màn hình: 14 inch | Pin: 4 cell / 81 Whr | Trọng lượng: 1.32 kg</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-79xf</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:09</t>
+          <t>2026-07-10 08:06:44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>48790000</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 7 350 ( 8 nhân, 12 luồng) Max. Boost Clock : Up to 5 GHz  Max Zen5c Clock : Up to 3.5 GHz, 8MB L2 Cache ; 16MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5060 with 8 GB of dedicated GDDR7 VRAM, supporting 3328 NVIDIA® CUDA® Cores | Màn hình: 16" FHD+ (1920x1200) IPS sRGB100% 180Hz, 400nits, 100% sRGB, Acer ComfyView™ LED-backlit TFT LCD,Grey to Grey 3 ms by Overdrive,Nvidia Advanced Optimus capable, Wide viewing angle.Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C  1x USB Type-C™ port supporting:  • USB4® 40Gbps  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    1x USB Type-C™ port, supporting:  • USB 3.2 Gen 2 (up to 10 Gbps)  • DisplayPort over USB-C  • USB charging 5 V; 3 A  • DC-in port 20 V; 90 W    Total 3x USB Standard A  3x USB Standard-A ports, supporting:  • 1x port for USB 2.0  • 1x port for USB 3.2 Gen 2  • 1x port for USB 3.2 Gen 2 featuring power off USB charging   1x HDMI® 2.1 port with HDCP support  1x microSD™ Card reader  1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone  1x Ethernet (RJ-45) port  1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, Loudness, Speaker | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: 1080p HD video at 60 fps with Temporal Noise Reduction | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.1 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:21</t>
+          <t>2026-07-10 08:06:56</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R193 (Ryzen 9 365/ RTX 5070/ 16GB/ 512GB/ 16.0" 2K/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>59490000</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>64390000</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁 Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen™ AI 9 365 ( 10 nhân 20 luồng) Up to 5 GHz, 10MB L2 Cache ; 24MB L3 Cache, Up to 50 TOPS | Ram: 16GB (1x16GB) DDR5 5600MHz (2x SO-DIMM socket, up to 96GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SSD (Còn trống 1 khe SSD M.2 PCIE, nâng cấp tối đa 4TB) | Card đồ họa: NVIDIA® GeForce RTX™ 5070 with 8 GB of dedicated GDDR7 VRAM, supporting 4608 NVIDIA® CUDA Cores | Màn hình: 16" 2K+ IPS sRGB100% 180Hz, 400nits, sRGB 100%, High-brightness Acer ComfyView™ LED-backlit TFT LCD, supporting 180 Hz, 3 ms (GTG) via LCD overdrive, Nvidia Advanced Optimus capable.16:10 aspect ratio, sRGB 100%(Typical value) Wide viewing angle Ultra-slim design | Cổng giao tiếp: Total 2x USB Type-C 1x USB Type-C™ port supporting: • USB4® 40Gbps • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W 1x USB Type-C™ port, supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • DisplayPort over USB-C • USB charging 5 V; 3 A • DC-in port 20 V; 90 W Total 3x USB Standard A 3x USB Standard-A ports, supporting: • 1x port for USB 2.0 • 1x port for USB 3.2 Gen 2 • 1x port for USB 3.2 Gen 2 featuring power off USB charging 1x HDMI® 2.1 port with HDCP support 1x microSD™ Card reader 1x 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone 1x Ethernet (RJ-45) port 1x DC-in jack for AC adapter | Audio: DTS® X:Ultra Audio, featuring optimized Bass, | Bàn phím: Bàn phím số, 4-Zone RGB | Tản nhiệt: Dual-Fan  Quad Intake  Quad-Exhaust  Liquid metal thermal grease | Chuẩn LAN: Killer™ Ethernet E3100G | Chuẩn WIFI: 802.11 a/b/g/n/ac/ax | Bluetooth: Bluetooth® 5.3 | Webcam: Narrow USB FHD camera+IR camera with blue glass | Hệ điều hành: Windows 11 Home Single Language | Pin: 76Wh 4-cell Li-ion battery  230W AC Adapter | Trọng lượng: 2.18 kg | Màu sắc: Obsidian black | Chất liệu: Cover A, D : Aluminum  Cover B, C : Plastic | Kích thước: 356.78 (W) x 275.5 (D) x 12.14/19.9 (H) mm</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r193</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:33</t>
+          <t>2026-07-10 08:07:08</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/  RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>43890000</v>
+        <v>82990000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>50590000</v>
+        <v>83990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>CPU: AMD Ryzen AI 5 340 (6 lõi / 12 luồng, 2 GHz - 4.8 GHz, 6MB L2 Cache 16MB L3 Cache) | Card đồ họa: NVIDIA GeForce RTX 5060 8 GB GDDR7 VRAM, hỗ trợ 3328 NVIDIA CUDA Cores | Tính chất bề mặt: Acer | RAM: 16GB (1 x 16GB) DDR5 5200MHz (2x SO-DIMM socket, up to 94GB SDRAM) | SSD: 512GB PCIe NVMe SSD (Up to 4TB PCIe Gen4 NVMe SSD​) | Kích thước màn hình: 16 inch | Pin: 76Wh 4-cell Li-ion battery | Trọng lượng: 2.1 kg</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:46</t>
+          <t>2026-07-10 08:07:19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro Lite 16 NL16 71G 56WQ (I5-13420H/ RTX 3050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>24390000</v>
+        <v>86990000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>28190000</v>
+        <v>87990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>✔ Bảo hành chính hãng 24 tháng. | ✔ Hỗ trợ đổi mới trong 7 ngày. | ✔ Miễn phí giao hàng toàn quốc. | Quà tặng: | 🎁Balo Acer SUV | Hỗ trợ trả góp MPOS (Thẻ tín dụng), HDSAISON ( | Xem chi tiết | ).</t>
-        </is>
-      </c>
+          <t>Giảm 2% (tối đa 500k) cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>CPU: Intel® Core™ i5-13420H (Upto 4.6 GHz/ 12MB/ 8 nhân, 12 luồng) | Ram: 16GB (8GB Onboard + 8GB Sodimm) DDR5 4800MHz (1x SO-DIMM socket, up to 56GB SDRAM) | Ổ cứng: 512GB PCIe NVMe SED SSD (Tổng 1 khe SSD M.2 PCIE, nâng cấp tối đa 2TB) | Card đồ họa: NVIDIA® GeForce® RTX™ 3050 with 6 GB of dedicated GDDR6 VRAM, supporting 2560 NVIDIA® CUDA® Cores. | Màn hình: 16" 16:10 WUXGA (1920x1200) IPS, 165Hz, 300nits, 45% NTSC,  Acer ComfyView™, LED-backlit TFT LCD, Wide viewing angle up to 170 degrees | Cổng giao tiếp: USB Type-C 1x USB Type-C™ port supporting: • USB 3.2 Gen 2 (up to 10 Gbps) • Thunderbolt™ 4 • USB charging 5 V; 3 A • DC-in port 20 V; 65 W USB Standard A 2x USB Standard-A ports, supporting: • One port for USB 3.2 Gen 1 • One port for USB 3.2 Gen 1 featuring power off USB charging 3.5 mm headphone/speaker jack, supporting headsets with built-in microphone HDMI®  2.1 port with HDCP support Ethernet (RJ-45) port | Audio: 2 speaker | Bàn phím: Đơn sắc - Trắng , có bàn phím số, Copilot Key | Tản nhiệt: 2 quạt | Chuẩn LAN: Có | Chuẩn WIFI: 802.11a/b/g/n/ac+ax wireless LAN | Bluetooth: Bluetooth® 5.0 | Webcam: FHD | Hệ điều hành: Windows 11 Home Single Language | Pin: 3 Cell 53WHr | Trọng lượng: 1.95 kg | Màu sắc: Trắng | Chất liệu: Cover A, B, C, D: Plastic | Kích thước: 362.2 (W) x 248.47 (D) x 22.9/22.9 (H) mm</t>
+          <t>CPU: Intel Core Ultra 9 386H (16 cores / 16 threads / up to 4.9GHz / 18MB Cache) Intel AI Boost NPU up to 50 TOPS | Card đồ họa: NVIDIA GeForce RTX 5070 8GB GDDR7 | RAM: 32GB (2 x 16GB) DDR5 7200MHz (2x SO-DIMM / up to 128GB) | SSD: 1TB SSD M.2 NVMe PCIe Gen4x4 (2 x M.2 NVMe PCIe Gen4) | Kích thước màn hình: 16 inch | Pin: 90Whr / 4-cell | Trọng lượng: 1.99 kg</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:18:58</t>
+          <t>2026-07-10 08:07:31</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-61M-R9RA (Ryzen AI 5 340/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>114890000</v>
+        <v>24490000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>129900000</v>
+        <v>26990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000₫) | Giảm 2% (t